--- a/WaDE Dataset Cleaning/Omitted_Samples.xlsx
+++ b/WaDE Dataset Cleaning/Omitted_Samples.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="317">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -29,10 +29,19 @@
     <t xml:space="preserve">Samples remaining after filtering</t>
   </si>
   <si>
-    <t xml:space="preserve">Variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N_missing_9999</t>
+    <t xml:space="preserve">Missing samples - Dry events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missing samples - Non-Dry events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample_ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flow_state</t>
   </si>
   <si>
     <t xml:space="preserve">Temp_C</t>
@@ -68,18 +77,15 @@
     <t xml:space="preserve">DIC_uM</t>
   </si>
   <si>
-    <t xml:space="preserve">Sample_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site</t>
-  </si>
-  <si>
     <t xml:space="preserve">WaDE_1</t>
   </si>
   <si>
     <t xml:space="preserve">BSL1.1</t>
   </si>
   <si>
+    <t xml:space="preserve">Flowing</t>
+  </si>
+  <si>
     <t xml:space="preserve">WaDE_2</t>
   </si>
   <si>
@@ -116,6 +122,9 @@
     <t xml:space="preserve">BSL4.1</t>
   </si>
   <si>
+    <t xml:space="preserve">Pooled</t>
+  </si>
+  <si>
     <t xml:space="preserve">WaDE_10</t>
   </si>
   <si>
@@ -303,6 +312,9 @@
   </si>
   <si>
     <t xml:space="preserve">NS_117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dry</t>
   </si>
   <si>
     <t xml:space="preserve">NS_118</t>
@@ -1311,1874 +1323,2407 @@
         <v>386</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>194</v>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="n">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="n">
-        <v>201</v>
+      <c r="B6" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" t="n">
-        <v>201</v>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" t="s">
+        <v>19</v>
+      </c>
+      <c r="N9" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="n">
-        <v>202</v>
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0561</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="G10" t="n">
+        <v>71.67</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1438</v>
+      </c>
+      <c r="I10" t="n">
+        <v>576</v>
+      </c>
+      <c r="J10" t="n">
+        <v>193</v>
+      </c>
+      <c r="K10" t="n">
+        <v>27</v>
+      </c>
+      <c r="L10" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>206</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-9999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="n">
-        <v>201</v>
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.00322</v>
+      </c>
+      <c r="G11" t="n">
+        <v>65</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1290</v>
+      </c>
+      <c r="I11" t="n">
+        <v>613</v>
+      </c>
+      <c r="J11" t="n">
+        <v>195</v>
+      </c>
+      <c r="K11" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="M11" t="n">
+        <v>161</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-9999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" t="n">
-        <v>201</v>
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0641</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.00741</v>
+      </c>
+      <c r="G12" t="n">
+        <v>134.17</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2029</v>
+      </c>
+      <c r="I12" t="n">
+        <v>389</v>
+      </c>
+      <c r="J12" t="n">
+        <v>288</v>
+      </c>
+      <c r="K12" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="L12" t="n">
+        <v>132</v>
+      </c>
+      <c r="M12" t="n">
+        <v>261</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-9999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="n">
-        <v>201</v>
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="G13" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="I13" t="n">
+        <v>640</v>
+      </c>
+      <c r="J13" t="n">
+        <v>144</v>
+      </c>
+      <c r="K13" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="M13" t="n">
+        <v>151</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-9999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="n">
-        <v>201</v>
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.0571</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.00275</v>
+      </c>
+      <c r="G14" t="n">
+        <v>34.17</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1079</v>
+      </c>
+      <c r="I14" t="n">
+        <v>646</v>
+      </c>
+      <c r="J14" t="n">
+        <v>135</v>
+      </c>
+      <c r="K14" t="n">
+        <v>29</v>
+      </c>
+      <c r="L14" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="M14" t="n">
+        <v>142</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-9999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="n">
-        <v>201</v>
+        <v>32</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.0322</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.00291</v>
+      </c>
+      <c r="G15" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1428</v>
+      </c>
+      <c r="I15" t="n">
+        <v>610</v>
+      </c>
+      <c r="J15" t="n">
+        <v>166</v>
+      </c>
+      <c r="K15" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>64</v>
+      </c>
+      <c r="M15" t="n">
+        <v>174</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-9999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" t="n">
-        <v>201</v>
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0947</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.00844</v>
+      </c>
+      <c r="G16" t="n">
+        <v>168.33</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3036</v>
+      </c>
+      <c r="I16" t="n">
+        <v>734</v>
+      </c>
+      <c r="J16" t="n">
+        <v>541</v>
+      </c>
+      <c r="K16" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="L16" t="n">
+        <v>190</v>
+      </c>
+      <c r="M16" t="n">
+        <v>520</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-9999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" t="n">
-        <v>243</v>
+        <v>37</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="G17" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>242</v>
+      </c>
+      <c r="I17" t="n">
+        <v>124</v>
+      </c>
+      <c r="J17" t="n">
+        <v>144</v>
+      </c>
+      <c r="K17" t="n">
+        <v>28</v>
+      </c>
+      <c r="L17" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="M17" t="n">
+        <v>137</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" t="n">
+        <v>15</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.00184</v>
+      </c>
+      <c r="G18" t="n">
+        <v>63.33</v>
+      </c>
+      <c r="H18" t="n">
+        <v>664</v>
+      </c>
+      <c r="I18" t="n">
+        <v>360</v>
+      </c>
+      <c r="J18" t="n">
+        <v>128</v>
+      </c>
+      <c r="K18" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>148</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-9999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.00254</v>
+      </c>
+      <c r="G19" t="n">
+        <v>86.67</v>
+      </c>
+      <c r="H19" t="n">
+        <v>641</v>
+      </c>
+      <c r="I19" t="n">
+        <v>337</v>
+      </c>
+      <c r="J19" t="n">
+        <v>75</v>
+      </c>
+      <c r="K19" t="n">
+        <v>21</v>
+      </c>
+      <c r="L19" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="M19" t="n">
+        <v>113</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-9999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H20" t="s">
-        <v>12</v>
-      </c>
-      <c r="I20" t="s">
-        <v>13</v>
-      </c>
-      <c r="J20" t="s">
-        <v>14</v>
-      </c>
-      <c r="K20" t="s">
-        <v>15</v>
-      </c>
-      <c r="L20" t="s">
-        <v>16</v>
-      </c>
-      <c r="M20" t="s">
-        <v>17</v>
+        <v>23</v>
+      </c>
+      <c r="D20" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.00258</v>
+      </c>
+      <c r="G20" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1348</v>
+      </c>
+      <c r="I20" t="n">
+        <v>400</v>
+      </c>
+      <c r="J20" t="n">
+        <v>119</v>
+      </c>
+      <c r="K20" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="M20" t="n">
+        <v>134</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-9999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" t="n">
-        <v>13.3</v>
+        <v>46</v>
+      </c>
+      <c r="C21" t="s">
+        <v>23</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0561</v>
+        <v>15.8</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0049</v>
+        <v>0.0366</v>
       </c>
       <c r="F21" t="n">
-        <v>71.67</v>
+        <v>0.00099</v>
       </c>
       <c r="G21" t="n">
-        <v>1438</v>
+        <v>47.5</v>
       </c>
       <c r="H21" t="n">
-        <v>576</v>
+        <v>429</v>
       </c>
       <c r="I21" t="n">
-        <v>193</v>
+        <v>369</v>
       </c>
       <c r="J21" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="K21" t="n">
-        <v>77.5</v>
+        <v>24.1</v>
       </c>
       <c r="L21" t="n">
-        <v>206</v>
+        <v>39.4</v>
       </c>
       <c r="M21" t="n">
+        <v>96</v>
+      </c>
+      <c r="N21" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="B22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" t="s">
         <v>23</v>
       </c>
-      <c r="C22" t="n">
-        <v>13.9</v>
-      </c>
       <c r="D22" t="n">
-        <v>0.064</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="n">
-        <v>0.00322</v>
+        <v>0.115</v>
       </c>
       <c r="F22" t="n">
-        <v>65</v>
+        <v>0.0153</v>
       </c>
       <c r="G22" t="n">
-        <v>1290</v>
+        <v>140</v>
       </c>
       <c r="H22" t="n">
-        <v>613</v>
+        <v>1262</v>
       </c>
       <c r="I22" t="n">
-        <v>195</v>
+        <v>440</v>
       </c>
       <c r="J22" t="n">
-        <v>26.6</v>
+        <v>459</v>
       </c>
       <c r="K22" t="n">
-        <v>54.7</v>
+        <v>74.4</v>
       </c>
       <c r="L22" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="M22" t="n">
+        <v>328</v>
+      </c>
+      <c r="N22" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" t="n">
-        <v>14.5</v>
+        <v>50</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0641</v>
+        <v>12.7</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00741</v>
+        <v>0.0272</v>
       </c>
       <c r="F23" t="n">
-        <v>134.17</v>
+        <v>0.00224</v>
       </c>
       <c r="G23" t="n">
-        <v>2029</v>
+        <v>96.67</v>
       </c>
       <c r="H23" t="n">
-        <v>389</v>
+        <v>1023</v>
       </c>
       <c r="I23" t="n">
-        <v>288</v>
+        <v>519</v>
       </c>
       <c r="J23" t="n">
-        <v>31.9</v>
+        <v>193</v>
       </c>
       <c r="K23" t="n">
-        <v>132</v>
+        <v>37.4</v>
       </c>
       <c r="L23" t="n">
-        <v>261</v>
+        <v>157</v>
       </c>
       <c r="M23" t="n">
+        <v>158</v>
+      </c>
+      <c r="N23" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" t="n">
-        <v>15.2</v>
+        <v>52</v>
+      </c>
+      <c r="C24" t="s">
+        <v>23</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0537</v>
+        <v>14.3</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00235</v>
+        <v>8.11</v>
       </c>
       <c r="F24" t="n">
-        <v>41.67</v>
+        <v>0.0198</v>
       </c>
       <c r="G24" t="n">
-        <v>1202</v>
+        <v>170.83</v>
       </c>
       <c r="H24" t="n">
-        <v>640</v>
+        <v>1332</v>
       </c>
       <c r="I24" t="n">
-        <v>144</v>
+        <v>458</v>
       </c>
       <c r="J24" t="n">
-        <v>26.2</v>
+        <v>594</v>
       </c>
       <c r="K24" t="n">
-        <v>45.7</v>
+        <v>100</v>
       </c>
       <c r="L24" t="n">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="M24" t="n">
+        <v>405</v>
+      </c>
+      <c r="N24" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" t="n">
-        <v>15.2</v>
+        <v>54</v>
+      </c>
+      <c r="C25" t="s">
+        <v>23</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0571</v>
+        <v>14.3</v>
       </c>
       <c r="E25" t="n">
-        <v>0.00275</v>
+        <v>0.15</v>
       </c>
       <c r="F25" t="n">
-        <v>34.17</v>
+        <v>0.0177</v>
       </c>
       <c r="G25" t="n">
-        <v>1079</v>
+        <v>172.5</v>
       </c>
       <c r="H25" t="n">
-        <v>646</v>
+        <v>1331</v>
       </c>
       <c r="I25" t="n">
-        <v>135</v>
+        <v>469</v>
       </c>
       <c r="J25" t="n">
-        <v>29</v>
+        <v>632</v>
       </c>
       <c r="K25" t="n">
-        <v>39.5</v>
+        <v>104</v>
       </c>
       <c r="L25" t="n">
-        <v>142</v>
+        <v>177</v>
       </c>
       <c r="M25" t="n">
+        <v>455</v>
+      </c>
+      <c r="N25" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" t="n">
-        <v>15.5</v>
+        <v>56</v>
+      </c>
+      <c r="C26" t="s">
+        <v>23</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0322</v>
+        <v>14.4</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00291</v>
+        <v>0.142</v>
       </c>
       <c r="F26" t="n">
-        <v>53.33</v>
+        <v>0.0168</v>
       </c>
       <c r="G26" t="n">
-        <v>1428</v>
+        <v>164.17</v>
       </c>
       <c r="H26" t="n">
-        <v>610</v>
+        <v>1363</v>
       </c>
       <c r="I26" t="n">
-        <v>166</v>
+        <v>503</v>
       </c>
       <c r="J26" t="n">
-        <v>21.3</v>
+        <v>620</v>
       </c>
       <c r="K26" t="n">
-        <v>64</v>
+        <v>98.6</v>
       </c>
       <c r="L26" t="n">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="M26" t="n">
+        <v>447</v>
+      </c>
+      <c r="N26" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" t="n">
-        <v>12.7</v>
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
+        <v>23</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0947</v>
+        <v>13.4</v>
       </c>
       <c r="E27" t="n">
-        <v>0.00844</v>
+        <v>0.0203</v>
       </c>
       <c r="F27" t="n">
-        <v>168.33</v>
+        <v>0.00156</v>
       </c>
       <c r="G27" t="n">
-        <v>3036</v>
+        <v>72.5</v>
       </c>
       <c r="H27" t="n">
-        <v>734</v>
+        <v>851</v>
       </c>
       <c r="I27" t="n">
-        <v>541</v>
+        <v>240</v>
       </c>
       <c r="J27" t="n">
-        <v>45.7</v>
+        <v>88</v>
       </c>
       <c r="K27" t="n">
-        <v>190</v>
+        <v>39</v>
       </c>
       <c r="L27" t="n">
-        <v>520</v>
+        <v>99.7</v>
       </c>
       <c r="M27" t="n">
+        <v>68</v>
+      </c>
+      <c r="N27" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" t="n">
-        <v>13.7</v>
+        <v>60</v>
+      </c>
+      <c r="C28" t="s">
+        <v>23</v>
       </c>
       <c r="D28" t="n">
-        <v>0.131</v>
+        <v>15.2</v>
       </c>
       <c r="E28" t="n">
-        <v>0.184</v>
+        <v>0.181</v>
       </c>
       <c r="F28" t="n">
-        <v>57.5</v>
+        <v>0.0192</v>
       </c>
       <c r="G28" t="n">
-        <v>242</v>
+        <v>182.5</v>
       </c>
       <c r="H28" t="n">
-        <v>124</v>
+        <v>1426</v>
       </c>
       <c r="I28" t="n">
-        <v>144</v>
+        <v>496</v>
       </c>
       <c r="J28" t="n">
-        <v>28</v>
+        <v>737</v>
       </c>
       <c r="K28" t="n">
-        <v>75.8</v>
+        <v>113</v>
       </c>
       <c r="L28" t="n">
-        <v>137</v>
+        <v>218</v>
       </c>
       <c r="M28" t="n">
+        <v>522</v>
+      </c>
+      <c r="N28" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" t="n">
-        <v>15</v>
+        <v>62</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0243</v>
+        <v>15.1</v>
       </c>
       <c r="E29" t="n">
-        <v>0.00184</v>
+        <v>0.0365</v>
       </c>
       <c r="F29" t="n">
-        <v>63.33</v>
+        <v>0.0383</v>
       </c>
       <c r="G29" t="n">
-        <v>664</v>
+        <v>101.67</v>
       </c>
       <c r="H29" t="n">
-        <v>360</v>
+        <v>1384</v>
       </c>
       <c r="I29" t="n">
-        <v>128</v>
+        <v>496</v>
       </c>
       <c r="J29" t="n">
-        <v>21.1</v>
+        <v>393</v>
       </c>
       <c r="K29" t="n">
-        <v>56.2</v>
+        <v>52.2</v>
       </c>
       <c r="L29" t="n">
-        <v>148</v>
+        <v>217</v>
       </c>
       <c r="M29" t="n">
+        <v>287</v>
+      </c>
+      <c r="N29" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" t="n">
-        <v>18.1</v>
+        <v>64</v>
+      </c>
+      <c r="C30" t="s">
+        <v>23</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0289</v>
+        <v>14.3</v>
       </c>
       <c r="E30" t="n">
-        <v>0.00254</v>
+        <v>0.025</v>
       </c>
       <c r="F30" t="n">
-        <v>86.67</v>
+        <v>0.00184</v>
       </c>
       <c r="G30" t="n">
-        <v>641</v>
+        <v>85.83</v>
       </c>
       <c r="H30" t="n">
-        <v>337</v>
+        <v>811</v>
       </c>
       <c r="I30" t="n">
-        <v>75</v>
+        <v>258</v>
       </c>
       <c r="J30" t="n">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="K30" t="n">
-        <v>33.4</v>
+        <v>52.2</v>
       </c>
       <c r="L30" t="n">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="M30" t="n">
+        <v>69</v>
+      </c>
+      <c r="N30" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
-      </c>
-      <c r="C31" t="n">
-        <v>15.4</v>
+        <v>66</v>
+      </c>
+      <c r="C31" t="s">
+        <v>23</v>
       </c>
       <c r="D31" t="n">
-        <v>0.012</v>
+        <v>15.2</v>
       </c>
       <c r="E31" t="n">
-        <v>0.00258</v>
+        <v>0.0465</v>
       </c>
       <c r="F31" t="n">
-        <v>58.33</v>
+        <v>0.017</v>
       </c>
       <c r="G31" t="n">
-        <v>1348</v>
+        <v>101.67</v>
       </c>
       <c r="H31" t="n">
-        <v>400</v>
+        <v>1553</v>
       </c>
       <c r="I31" t="n">
-        <v>119</v>
+        <v>586</v>
       </c>
       <c r="J31" t="n">
-        <v>23.5</v>
+        <v>483</v>
       </c>
       <c r="K31" t="n">
-        <v>50.7</v>
+        <v>54.9</v>
       </c>
       <c r="L31" t="n">
-        <v>134</v>
+        <v>258</v>
       </c>
       <c r="M31" t="n">
+        <v>362</v>
+      </c>
+      <c r="N31" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" t="n">
-        <v>15.8</v>
+        <v>68</v>
+      </c>
+      <c r="C32" t="s">
+        <v>23</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0366</v>
+        <v>15.9</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00099</v>
+        <v>0.0549</v>
       </c>
       <c r="F32" t="n">
-        <v>47.5</v>
+        <v>0.0177</v>
       </c>
       <c r="G32" t="n">
-        <v>429</v>
+        <v>92.5</v>
       </c>
       <c r="H32" t="n">
+        <v>1488</v>
+      </c>
+      <c r="I32" t="n">
+        <v>605</v>
+      </c>
+      <c r="J32" t="n">
+        <v>490</v>
+      </c>
+      <c r="K32" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="L32" t="n">
+        <v>267</v>
+      </c>
+      <c r="M32" t="n">
         <v>369</v>
       </c>
-      <c r="I32" t="n">
-        <v>70</v>
-      </c>
-      <c r="J32" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="K32" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="L32" t="n">
-        <v>96</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
-      </c>
-      <c r="C33" t="n">
-        <v>13.3</v>
+        <v>70</v>
+      </c>
+      <c r="C33" t="s">
+        <v>23</v>
       </c>
       <c r="D33" t="n">
-        <v>0.115</v>
+        <v>17.6</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0153</v>
+        <v>0.0715</v>
       </c>
       <c r="F33" t="n">
-        <v>140</v>
+        <v>0.0267</v>
       </c>
       <c r="G33" t="n">
-        <v>1262</v>
+        <v>110.83</v>
       </c>
       <c r="H33" t="n">
-        <v>440</v>
+        <v>1545</v>
       </c>
       <c r="I33" t="n">
-        <v>459</v>
+        <v>626</v>
       </c>
       <c r="J33" t="n">
-        <v>74.4</v>
+        <v>620</v>
       </c>
       <c r="K33" t="n">
-        <v>160</v>
+        <v>66.7</v>
       </c>
       <c r="L33" t="n">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="M33" t="n">
+        <v>442</v>
+      </c>
+      <c r="N33" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" t="n">
-        <v>12.7</v>
+        <v>72</v>
+      </c>
+      <c r="C34" t="s">
+        <v>23</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0272</v>
+        <v>19.4</v>
       </c>
       <c r="E34" t="n">
-        <v>0.00224</v>
+        <v>0.0483</v>
       </c>
       <c r="F34" t="n">
-        <v>96.67</v>
+        <v>0.00674</v>
       </c>
       <c r="G34" t="n">
-        <v>1023</v>
+        <v>75.83</v>
       </c>
       <c r="H34" t="n">
-        <v>519</v>
+        <v>1426</v>
       </c>
       <c r="I34" t="n">
-        <v>193</v>
+        <v>565</v>
       </c>
       <c r="J34" t="n">
-        <v>37.4</v>
+        <v>216</v>
       </c>
       <c r="K34" t="n">
-        <v>157</v>
+        <v>30.2</v>
       </c>
       <c r="L34" t="n">
-        <v>158</v>
+        <v>78.8</v>
       </c>
       <c r="M34" t="n">
+        <v>213</v>
+      </c>
+      <c r="N34" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35" t="n">
-        <v>14.3</v>
+        <v>74</v>
+      </c>
+      <c r="C35" t="s">
+        <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>8.11</v>
+        <v>17.8</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0198</v>
+        <v>0.0943</v>
       </c>
       <c r="F35" t="n">
-        <v>170.83</v>
+        <v>0.0139</v>
       </c>
       <c r="G35" t="n">
-        <v>1332</v>
+        <v>185.83</v>
       </c>
       <c r="H35" t="n">
-        <v>458</v>
+        <v>1131</v>
       </c>
       <c r="I35" t="n">
-        <v>594</v>
+        <v>438</v>
       </c>
       <c r="J35" t="n">
-        <v>100</v>
+        <v>582</v>
       </c>
       <c r="K35" t="n">
-        <v>160</v>
+        <v>39.8</v>
       </c>
       <c r="L35" t="n">
-        <v>405</v>
+        <v>84.5</v>
       </c>
       <c r="M35" t="n">
+        <v>282</v>
+      </c>
+      <c r="N35" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" t="n">
-        <v>14.3</v>
+        <v>76</v>
+      </c>
+      <c r="C36" t="s">
+        <v>23</v>
       </c>
       <c r="D36" t="n">
-        <v>0.15</v>
+        <v>20.1</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0177</v>
+        <v>0.0338</v>
       </c>
       <c r="F36" t="n">
-        <v>172.5</v>
+        <v>0.00404</v>
       </c>
       <c r="G36" t="n">
-        <v>1331</v>
+        <v>35</v>
       </c>
       <c r="H36" t="n">
-        <v>469</v>
+        <v>1155</v>
       </c>
       <c r="I36" t="n">
-        <v>632</v>
+        <v>565</v>
       </c>
       <c r="J36" t="n">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="K36" t="n">
-        <v>177</v>
+        <v>28.7</v>
       </c>
       <c r="L36" t="n">
-        <v>455</v>
+        <v>53.7</v>
       </c>
       <c r="M36" t="n">
+        <v>180</v>
+      </c>
+      <c r="N36" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" t="n">
-        <v>14.4</v>
+        <v>78</v>
+      </c>
+      <c r="C37" t="s">
+        <v>23</v>
       </c>
       <c r="D37" t="n">
-        <v>0.142</v>
+        <v>15</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0168</v>
+        <v>0.0579</v>
       </c>
       <c r="F37" t="n">
-        <v>164.17</v>
+        <v>0.00259</v>
       </c>
       <c r="G37" t="n">
-        <v>1363</v>
+        <v>71.67</v>
       </c>
       <c r="H37" t="n">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="I37" t="n">
-        <v>620</v>
+        <v>375</v>
       </c>
       <c r="J37" t="n">
-        <v>98.6</v>
+        <v>119</v>
       </c>
       <c r="K37" t="n">
-        <v>187</v>
+        <v>29.7</v>
       </c>
       <c r="L37" t="n">
-        <v>447</v>
+        <v>29.4</v>
       </c>
       <c r="M37" t="n">
+        <v>122</v>
+      </c>
+      <c r="N37" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B38" t="s">
-        <v>55</v>
-      </c>
-      <c r="C38" t="n">
-        <v>13.4</v>
+        <v>80</v>
+      </c>
+      <c r="C38" t="s">
+        <v>23</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0203</v>
+        <v>18.2</v>
       </c>
       <c r="E38" t="n">
-        <v>0.00156</v>
+        <v>0.163</v>
       </c>
       <c r="F38" t="n">
-        <v>72.5</v>
+        <v>0.00225</v>
       </c>
       <c r="G38" t="n">
-        <v>851</v>
+        <v>87.5</v>
       </c>
       <c r="H38" t="n">
-        <v>240</v>
+        <v>1475</v>
       </c>
       <c r="I38" t="n">
-        <v>88</v>
+        <v>296</v>
       </c>
       <c r="J38" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K38" t="n">
-        <v>99.7</v>
+        <v>20.1</v>
       </c>
       <c r="L38" t="n">
-        <v>68</v>
+        <v>31.3</v>
       </c>
       <c r="M38" t="n">
+        <v>52</v>
+      </c>
+      <c r="N38" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" t="n">
-        <v>15.2</v>
+        <v>82</v>
+      </c>
+      <c r="C39" t="s">
+        <v>23</v>
       </c>
       <c r="D39" t="n">
-        <v>0.181</v>
+        <v>16.4</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0192</v>
+        <v>0.0389</v>
       </c>
       <c r="F39" t="n">
-        <v>182.5</v>
+        <v>0.00155</v>
       </c>
       <c r="G39" t="n">
-        <v>1426</v>
+        <v>53.33</v>
       </c>
       <c r="H39" t="n">
-        <v>496</v>
+        <v>219</v>
       </c>
       <c r="I39" t="n">
-        <v>737</v>
+        <v>199</v>
       </c>
       <c r="J39" t="n">
-        <v>113</v>
+        <v>23</v>
       </c>
       <c r="K39" t="n">
-        <v>218</v>
+        <v>17.7</v>
       </c>
       <c r="L39" t="n">
-        <v>522</v>
+        <v>22.7</v>
       </c>
       <c r="M39" t="n">
+        <v>53</v>
+      </c>
+      <c r="N39" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="B40" t="s">
-        <v>59</v>
-      </c>
-      <c r="C40" t="n">
-        <v>15.1</v>
+        <v>84</v>
+      </c>
+      <c r="C40" t="s">
+        <v>23</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0365</v>
+        <v>13.4</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0383</v>
+        <v>0.0468</v>
       </c>
       <c r="F40" t="n">
-        <v>101.67</v>
+        <v>0.000407</v>
       </c>
       <c r="G40" t="n">
-        <v>1384</v>
+        <v>30</v>
       </c>
       <c r="H40" t="n">
-        <v>496</v>
+        <v>724</v>
       </c>
       <c r="I40" t="n">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="J40" t="n">
-        <v>52.2</v>
+        <v>165</v>
       </c>
       <c r="K40" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="L40" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="M40" t="n">
         <v>217</v>
       </c>
-      <c r="L40" t="n">
-        <v>287</v>
-      </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
-      </c>
-      <c r="C41" t="n">
-        <v>14.3</v>
+        <v>86</v>
+      </c>
+      <c r="C41" t="s">
+        <v>36</v>
       </c>
       <c r="D41" t="n">
-        <v>0.025</v>
+        <v>23.2</v>
       </c>
       <c r="E41" t="n">
-        <v>0.00184</v>
+        <v>0.287</v>
       </c>
       <c r="F41" t="n">
-        <v>85.83</v>
+        <v>0.0453</v>
       </c>
       <c r="G41" t="n">
-        <v>811</v>
+        <v>632.5</v>
       </c>
       <c r="H41" t="n">
-        <v>258</v>
+        <v>697</v>
       </c>
       <c r="I41" t="n">
-        <v>116</v>
+        <v>165</v>
       </c>
       <c r="J41" t="n">
-        <v>52.2</v>
+        <v>65</v>
       </c>
       <c r="K41" t="n">
-        <v>102</v>
+        <v>71.3</v>
       </c>
       <c r="L41" t="n">
-        <v>69</v>
+        <v>23.5</v>
       </c>
       <c r="M41" t="n">
+        <v>45</v>
+      </c>
+      <c r="N41" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="B42" t="s">
-        <v>63</v>
-      </c>
-      <c r="C42" t="n">
-        <v>15.2</v>
+        <v>54</v>
+      </c>
+      <c r="C42" t="s">
+        <v>23</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0465</v>
+        <v>7.6</v>
       </c>
       <c r="E42" t="n">
-        <v>0.017</v>
+        <v>0.184</v>
       </c>
       <c r="F42" t="n">
-        <v>101.67</v>
+        <v>0.024</v>
       </c>
       <c r="G42" t="n">
-        <v>1553</v>
+        <v>242.51</v>
       </c>
       <c r="H42" t="n">
-        <v>586</v>
+        <v>1351</v>
       </c>
       <c r="I42" t="n">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="J42" t="n">
-        <v>54.9</v>
+        <v>789</v>
       </c>
       <c r="K42" t="n">
-        <v>258</v>
+        <v>107</v>
       </c>
       <c r="L42" t="n">
-        <v>362</v>
+        <v>221</v>
       </c>
       <c r="M42" t="n">
+        <v>661</v>
+      </c>
+      <c r="N42" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="B43" t="s">
-        <v>65</v>
-      </c>
-      <c r="C43" t="n">
-        <v>15.9</v>
+        <v>68</v>
+      </c>
+      <c r="C43" t="s">
+        <v>23</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0549</v>
+        <v>7.42</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0177</v>
+        <v>0.101</v>
       </c>
       <c r="F43" t="n">
-        <v>92.5</v>
+        <v>0.0214</v>
       </c>
       <c r="G43" t="n">
-        <v>1488</v>
+        <v>107.11</v>
       </c>
       <c r="H43" t="n">
-        <v>605</v>
+        <v>1424</v>
       </c>
       <c r="I43" t="n">
-        <v>490</v>
+        <v>585</v>
       </c>
       <c r="J43" t="n">
-        <v>55.5</v>
+        <v>497</v>
       </c>
       <c r="K43" t="n">
-        <v>267</v>
+        <v>54.3</v>
       </c>
       <c r="L43" t="n">
-        <v>369</v>
+        <v>317</v>
       </c>
       <c r="M43" t="n">
+        <v>384</v>
+      </c>
+      <c r="N43" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="B44" t="s">
-        <v>67</v>
-      </c>
-      <c r="C44" t="n">
-        <v>17.6</v>
+        <v>72</v>
+      </c>
+      <c r="C44" t="s">
+        <v>23</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0715</v>
+        <v>7.62</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0267</v>
+        <v>0.0657</v>
       </c>
       <c r="F44" t="n">
-        <v>110.83</v>
+        <v>0.0105</v>
       </c>
       <c r="G44" t="n">
-        <v>1545</v>
+        <v>115.88</v>
       </c>
       <c r="H44" t="n">
-        <v>626</v>
+        <v>1526</v>
       </c>
       <c r="I44" t="n">
-        <v>620</v>
+        <v>586</v>
       </c>
       <c r="J44" t="n">
-        <v>66.7</v>
+        <v>204</v>
       </c>
       <c r="K44" t="n">
-        <v>354</v>
+        <v>33</v>
       </c>
       <c r="L44" t="n">
-        <v>442</v>
+        <v>108</v>
       </c>
       <c r="M44" t="n">
+        <v>200</v>
+      </c>
+      <c r="N44" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="B45" t="s">
-        <v>69</v>
-      </c>
-      <c r="C45" t="n">
-        <v>19.4</v>
+        <v>31</v>
+      </c>
+      <c r="C45" t="s">
+        <v>23</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0483</v>
+        <v>13.6</v>
       </c>
       <c r="E45" t="n">
-        <v>0.00674</v>
+        <v>0.0895</v>
       </c>
       <c r="F45" t="n">
-        <v>75.83</v>
+        <v>0.00273</v>
       </c>
       <c r="G45" t="n">
-        <v>1426</v>
+        <v>29.82</v>
       </c>
       <c r="H45" t="n">
-        <v>565</v>
+        <v>1101</v>
       </c>
       <c r="I45" t="n">
-        <v>216</v>
+        <v>771</v>
       </c>
       <c r="J45" t="n">
-        <v>30.2</v>
+        <v>116</v>
       </c>
       <c r="K45" t="n">
-        <v>78.8</v>
+        <v>29.5</v>
       </c>
       <c r="L45" t="n">
-        <v>213</v>
+        <v>38</v>
       </c>
       <c r="M45" t="n">
+        <v>129</v>
+      </c>
+      <c r="N45" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
-      </c>
-      <c r="C46" t="n">
-        <v>17.8</v>
+        <v>27</v>
+      </c>
+      <c r="C46" t="s">
+        <v>23</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0943</v>
+        <v>9.16</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0139</v>
+        <v>0.112</v>
       </c>
       <c r="F46" t="n">
-        <v>185.83</v>
+        <v>0.00809</v>
       </c>
       <c r="G46" t="n">
-        <v>1131</v>
+        <v>103.44</v>
       </c>
       <c r="H46" t="n">
-        <v>438</v>
+        <v>1746</v>
       </c>
       <c r="I46" t="n">
-        <v>582</v>
+        <v>410</v>
       </c>
       <c r="J46" t="n">
-        <v>39.8</v>
+        <v>267</v>
       </c>
       <c r="K46" t="n">
-        <v>84.5</v>
+        <v>35.7</v>
       </c>
       <c r="L46" t="n">
-        <v>282</v>
+        <v>167</v>
       </c>
       <c r="M46" t="n">
+        <v>248</v>
+      </c>
+      <c r="N46" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="B47" t="s">
-        <v>73</v>
-      </c>
-      <c r="C47" t="n">
-        <v>20.1</v>
+        <v>25</v>
+      </c>
+      <c r="C47" t="s">
+        <v>23</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0338</v>
+        <v>9.98</v>
       </c>
       <c r="E47" t="n">
-        <v>0.00404</v>
+        <v>0.0797</v>
       </c>
       <c r="F47" t="n">
-        <v>35</v>
+        <v>0.00389</v>
       </c>
       <c r="G47" t="n">
-        <v>1155</v>
+        <v>62.82</v>
       </c>
       <c r="H47" t="n">
-        <v>565</v>
+        <v>1331</v>
       </c>
       <c r="I47" t="n">
-        <v>176</v>
+        <v>681</v>
       </c>
       <c r="J47" t="n">
-        <v>28.7</v>
+        <v>156</v>
       </c>
       <c r="K47" t="n">
-        <v>53.7</v>
+        <v>30.2</v>
       </c>
       <c r="L47" t="n">
-        <v>180</v>
+        <v>67.1</v>
       </c>
       <c r="M47" t="n">
+        <v>161</v>
+      </c>
+      <c r="N47" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="B48" t="s">
-        <v>75</v>
-      </c>
-      <c r="C48" t="n">
-        <v>15</v>
+        <v>72</v>
+      </c>
+      <c r="C48" t="s">
+        <v>23</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0579</v>
+        <v>16.9</v>
       </c>
       <c r="E48" t="n">
-        <v>0.00259</v>
+        <v>0.202</v>
       </c>
       <c r="F48" t="n">
-        <v>71.67</v>
+        <v>0.0673</v>
       </c>
       <c r="G48" t="n">
-        <v>489</v>
+        <v>1003.72</v>
       </c>
       <c r="H48" t="n">
-        <v>375</v>
+        <v>659</v>
       </c>
       <c r="I48" t="n">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="J48" t="n">
-        <v>29.7</v>
+        <v>274</v>
       </c>
       <c r="K48" t="n">
-        <v>29.4</v>
+        <v>47.6</v>
       </c>
       <c r="L48" t="n">
-        <v>122</v>
+        <v>74.2</v>
       </c>
       <c r="M48" t="n">
+        <v>265</v>
+      </c>
+      <c r="N48" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B49" t="s">
-        <v>77</v>
-      </c>
-      <c r="C49" t="n">
-        <v>18.2</v>
+        <v>54</v>
+      </c>
+      <c r="C49" t="s">
+        <v>23</v>
       </c>
       <c r="D49" t="n">
-        <v>0.163</v>
+        <v>23.9</v>
       </c>
       <c r="E49" t="n">
-        <v>0.00225</v>
+        <v>0.13</v>
       </c>
       <c r="F49" t="n">
-        <v>87.5</v>
+        <v>0.0382</v>
       </c>
       <c r="G49" t="n">
-        <v>1475</v>
+        <v>202.49</v>
       </c>
       <c r="H49" t="n">
-        <v>296</v>
+        <v>1457</v>
       </c>
       <c r="I49" t="n">
-        <v>38</v>
+        <v>594</v>
       </c>
       <c r="J49" t="n">
-        <v>20.1</v>
+        <v>770</v>
       </c>
       <c r="K49" t="n">
-        <v>31.3</v>
+        <v>103</v>
       </c>
       <c r="L49" t="n">
-        <v>52</v>
+        <v>260</v>
       </c>
       <c r="M49" t="n">
+        <v>648</v>
+      </c>
+      <c r="N49" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="B50" t="s">
-        <v>79</v>
-      </c>
-      <c r="C50" t="n">
-        <v>16.4</v>
+        <v>96</v>
+      </c>
+      <c r="C50" t="s">
+        <v>23</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0389</v>
+        <v>24.5</v>
       </c>
       <c r="E50" t="n">
-        <v>0.00155</v>
+        <v>0.0784</v>
       </c>
       <c r="F50" t="n">
-        <v>53.33</v>
+        <v>0.0423</v>
       </c>
       <c r="G50" t="n">
-        <v>219</v>
+        <v>60.82</v>
       </c>
       <c r="H50" t="n">
-        <v>199</v>
+        <v>1414</v>
       </c>
       <c r="I50" t="n">
-        <v>23</v>
+        <v>620</v>
       </c>
       <c r="J50" t="n">
-        <v>17.7</v>
+        <v>338</v>
       </c>
       <c r="K50" t="n">
-        <v>22.7</v>
+        <v>29.8</v>
       </c>
       <c r="L50" t="n">
-        <v>53</v>
+        <v>38.1</v>
       </c>
       <c r="M50" t="n">
+        <v>954</v>
+      </c>
+      <c r="N50" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="B51" t="s">
-        <v>81</v>
-      </c>
-      <c r="C51" t="n">
-        <v>13.4</v>
+        <v>98</v>
+      </c>
+      <c r="C51" t="s">
+        <v>23</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0468</v>
+        <v>9.82</v>
       </c>
       <c r="E51" t="n">
-        <v>0.000407</v>
+        <v>0.0227</v>
       </c>
       <c r="F51" t="n">
-        <v>30</v>
+        <v>0.00212</v>
       </c>
       <c r="G51" t="n">
-        <v>724</v>
+        <v>-9999</v>
       </c>
       <c r="H51" t="n">
-        <v>378</v>
+        <v>849</v>
       </c>
       <c r="I51" t="n">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="J51" t="n">
-        <v>20.5</v>
+        <v>113</v>
       </c>
       <c r="K51" t="n">
-        <v>32.1</v>
+        <v>35.2</v>
       </c>
       <c r="L51" t="n">
-        <v>217</v>
+        <v>127</v>
       </c>
       <c r="M51" t="n">
+        <v>92</v>
+      </c>
+      <c r="N51" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="B52" t="s">
-        <v>83</v>
-      </c>
-      <c r="C52" t="n">
-        <v>23.2</v>
+        <v>35</v>
+      </c>
+      <c r="C52" t="s">
+        <v>100</v>
       </c>
       <c r="D52" t="n">
-        <v>0.287</v>
+        <v>-9999</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0453</v>
+        <v>-9999</v>
       </c>
       <c r="F52" t="n">
-        <v>632.5</v>
+        <v>-9999</v>
       </c>
       <c r="G52" t="n">
-        <v>697</v>
+        <v>-9999</v>
       </c>
       <c r="H52" t="n">
-        <v>165</v>
+        <v>-9999</v>
       </c>
       <c r="I52" t="n">
-        <v>65</v>
+        <v>-9999</v>
       </c>
       <c r="J52" t="n">
-        <v>71.3</v>
+        <v>-9999</v>
       </c>
       <c r="K52" t="n">
-        <v>23.5</v>
+        <v>-9999</v>
       </c>
       <c r="L52" t="n">
-        <v>45</v>
+        <v>-9999</v>
       </c>
       <c r="M52" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N52" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="B53" t="s">
-        <v>51</v>
-      </c>
-      <c r="C53" t="n">
-        <v>7.6</v>
+        <v>35</v>
+      </c>
+      <c r="C53" t="s">
+        <v>100</v>
       </c>
       <c r="D53" t="n">
-        <v>0.184</v>
+        <v>-9999</v>
       </c>
       <c r="E53" t="n">
-        <v>0.024</v>
+        <v>-9999</v>
       </c>
       <c r="F53" t="n">
-        <v>242.51</v>
+        <v>-9999</v>
       </c>
       <c r="G53" t="n">
-        <v>1351</v>
+        <v>-9999</v>
       </c>
       <c r="H53" t="n">
-        <v>504</v>
+        <v>-9999</v>
       </c>
       <c r="I53" t="n">
-        <v>789</v>
+        <v>-9999</v>
       </c>
       <c r="J53" t="n">
-        <v>107</v>
+        <v>-9999</v>
       </c>
       <c r="K53" t="n">
-        <v>221</v>
+        <v>-9999</v>
       </c>
       <c r="L53" t="n">
-        <v>661</v>
+        <v>-9999</v>
       </c>
       <c r="M53" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N53" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="B54" t="s">
-        <v>65</v>
-      </c>
-      <c r="C54" t="n">
-        <v>7.42</v>
+        <v>35</v>
+      </c>
+      <c r="C54" t="s">
+        <v>100</v>
       </c>
       <c r="D54" t="n">
-        <v>0.101</v>
+        <v>-9999</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0214</v>
+        <v>-9999</v>
       </c>
       <c r="F54" t="n">
-        <v>107.11</v>
+        <v>-9999</v>
       </c>
       <c r="G54" t="n">
-        <v>1424</v>
+        <v>-9999</v>
       </c>
       <c r="H54" t="n">
-        <v>585</v>
+        <v>-9999</v>
       </c>
       <c r="I54" t="n">
-        <v>497</v>
+        <v>-9999</v>
       </c>
       <c r="J54" t="n">
-        <v>54.3</v>
+        <v>-9999</v>
       </c>
       <c r="K54" t="n">
-        <v>317</v>
+        <v>-9999</v>
       </c>
       <c r="L54" t="n">
-        <v>384</v>
+        <v>-9999</v>
       </c>
       <c r="M54" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N54" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B55" t="s">
-        <v>69</v>
-      </c>
-      <c r="C55" t="n">
-        <v>7.62</v>
+        <v>35</v>
+      </c>
+      <c r="C55" t="s">
+        <v>100</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0657</v>
+        <v>-9999</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0105</v>
+        <v>-9999</v>
       </c>
       <c r="F55" t="n">
-        <v>115.88</v>
+        <v>-9999</v>
       </c>
       <c r="G55" t="n">
-        <v>1526</v>
+        <v>-9999</v>
       </c>
       <c r="H55" t="n">
-        <v>586</v>
+        <v>-9999</v>
       </c>
       <c r="I55" t="n">
-        <v>204</v>
+        <v>-9999</v>
       </c>
       <c r="J55" t="n">
-        <v>33</v>
+        <v>-9999</v>
       </c>
       <c r="K55" t="n">
-        <v>108</v>
+        <v>-9999</v>
       </c>
       <c r="L55" t="n">
-        <v>200</v>
+        <v>-9999</v>
       </c>
       <c r="M55" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N55" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="B56" t="s">
-        <v>29</v>
-      </c>
-      <c r="C56" t="n">
-        <v>13.6</v>
+        <v>105</v>
+      </c>
+      <c r="C56" t="s">
+        <v>100</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0895</v>
+        <v>-9999</v>
       </c>
       <c r="E56" t="n">
-        <v>0.00273</v>
+        <v>-9999</v>
       </c>
       <c r="F56" t="n">
-        <v>29.82</v>
+        <v>-9999</v>
       </c>
       <c r="G56" t="n">
-        <v>1101</v>
+        <v>-9999</v>
       </c>
       <c r="H56" t="n">
-        <v>771</v>
+        <v>-9999</v>
       </c>
       <c r="I56" t="n">
-        <v>116</v>
+        <v>-9999</v>
       </c>
       <c r="J56" t="n">
-        <v>29.5</v>
+        <v>-9999</v>
       </c>
       <c r="K56" t="n">
-        <v>38</v>
+        <v>-9999</v>
       </c>
       <c r="L56" t="n">
-        <v>129</v>
+        <v>-9999</v>
       </c>
       <c r="M56" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N56" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B57" t="s">
-        <v>25</v>
-      </c>
-      <c r="C57" t="n">
-        <v>9.16</v>
+        <v>105</v>
+      </c>
+      <c r="C57" t="s">
+        <v>100</v>
       </c>
       <c r="D57" t="n">
-        <v>0.112</v>
+        <v>-9999</v>
       </c>
       <c r="E57" t="n">
-        <v>0.00809</v>
+        <v>-9999</v>
       </c>
       <c r="F57" t="n">
-        <v>103.44</v>
+        <v>-9999</v>
       </c>
       <c r="G57" t="n">
-        <v>1746</v>
+        <v>-9999</v>
       </c>
       <c r="H57" t="n">
-        <v>410</v>
+        <v>-9999</v>
       </c>
       <c r="I57" t="n">
-        <v>267</v>
+        <v>-9999</v>
       </c>
       <c r="J57" t="n">
-        <v>35.7</v>
+        <v>-9999</v>
       </c>
       <c r="K57" t="n">
-        <v>167</v>
+        <v>-9999</v>
       </c>
       <c r="L57" t="n">
-        <v>248</v>
+        <v>-9999</v>
       </c>
       <c r="M57" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N57" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B58" t="s">
-        <v>23</v>
-      </c>
-      <c r="C58" t="n">
-        <v>9.98</v>
+        <v>105</v>
+      </c>
+      <c r="C58" t="s">
+        <v>100</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0797</v>
+        <v>-9999</v>
       </c>
       <c r="E58" t="n">
-        <v>0.00389</v>
+        <v>-9999</v>
       </c>
       <c r="F58" t="n">
-        <v>62.82</v>
+        <v>-9999</v>
       </c>
       <c r="G58" t="n">
-        <v>1331</v>
+        <v>-9999</v>
       </c>
       <c r="H58" t="n">
-        <v>681</v>
+        <v>-9999</v>
       </c>
       <c r="I58" t="n">
-        <v>156</v>
+        <v>-9999</v>
       </c>
       <c r="J58" t="n">
-        <v>30.2</v>
+        <v>-9999</v>
       </c>
       <c r="K58" t="n">
-        <v>67.1</v>
+        <v>-9999</v>
       </c>
       <c r="L58" t="n">
-        <v>161</v>
+        <v>-9999</v>
       </c>
       <c r="M58" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N58" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="B59" t="s">
-        <v>69</v>
-      </c>
-      <c r="C59" t="n">
-        <v>16.9</v>
+        <v>105</v>
+      </c>
+      <c r="C59" t="s">
+        <v>100</v>
       </c>
       <c r="D59" t="n">
-        <v>0.202</v>
+        <v>-9999</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0673</v>
+        <v>-9999</v>
       </c>
       <c r="F59" t="n">
-        <v>1003.72</v>
+        <v>-9999</v>
       </c>
       <c r="G59" t="n">
-        <v>659</v>
+        <v>-9999</v>
       </c>
       <c r="H59" t="n">
-        <v>153</v>
+        <v>-9999</v>
       </c>
       <c r="I59" t="n">
-        <v>274</v>
+        <v>-9999</v>
       </c>
       <c r="J59" t="n">
-        <v>47.6</v>
+        <v>-9999</v>
       </c>
       <c r="K59" t="n">
-        <v>74.2</v>
+        <v>-9999</v>
       </c>
       <c r="L59" t="n">
-        <v>265</v>
+        <v>-9999</v>
       </c>
       <c r="M59" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N59" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="B60" t="s">
-        <v>51</v>
-      </c>
-      <c r="C60" t="n">
-        <v>23.9</v>
+        <v>105</v>
+      </c>
+      <c r="C60" t="s">
+        <v>100</v>
       </c>
       <c r="D60" t="n">
-        <v>0.13</v>
+        <v>-9999</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0382</v>
+        <v>-9999</v>
       </c>
       <c r="F60" t="n">
-        <v>202.49</v>
+        <v>-9999</v>
       </c>
       <c r="G60" t="n">
-        <v>1457</v>
+        <v>-9999</v>
       </c>
       <c r="H60" t="n">
-        <v>594</v>
+        <v>-9999</v>
       </c>
       <c r="I60" t="n">
-        <v>770</v>
+        <v>-9999</v>
       </c>
       <c r="J60" t="n">
-        <v>103</v>
+        <v>-9999</v>
       </c>
       <c r="K60" t="n">
-        <v>260</v>
+        <v>-9999</v>
       </c>
       <c r="L60" t="n">
-        <v>648</v>
+        <v>-9999</v>
       </c>
       <c r="M60" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N60" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="B61" t="s">
-        <v>93</v>
-      </c>
-      <c r="C61" t="n">
-        <v>24.5</v>
+        <v>105</v>
+      </c>
+      <c r="C61" t="s">
+        <v>100</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0784</v>
+        <v>-9999</v>
       </c>
       <c r="E61" t="n">
-        <v>0.0423</v>
+        <v>-9999</v>
       </c>
       <c r="F61" t="n">
-        <v>60.82</v>
+        <v>-9999</v>
       </c>
       <c r="G61" t="n">
-        <v>1414</v>
+        <v>-9999</v>
       </c>
       <c r="H61" t="n">
-        <v>620</v>
+        <v>-9999</v>
       </c>
       <c r="I61" t="n">
-        <v>338</v>
+        <v>-9999</v>
       </c>
       <c r="J61" t="n">
-        <v>29.8</v>
+        <v>-9999</v>
       </c>
       <c r="K61" t="n">
-        <v>38.1</v>
+        <v>-9999</v>
       </c>
       <c r="L61" t="n">
-        <v>954</v>
+        <v>-9999</v>
       </c>
       <c r="M61" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N61" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="B62" t="s">
-        <v>95</v>
-      </c>
-      <c r="C62" t="n">
-        <v>9.82</v>
+        <v>112</v>
+      </c>
+      <c r="C62" t="s">
+        <v>100</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0227</v>
+        <v>-9999</v>
       </c>
       <c r="E62" t="n">
-        <v>0.00212</v>
+        <v>-9999</v>
       </c>
       <c r="F62" t="n">
         <v>-9999</v>
       </c>
       <c r="G62" t="n">
-        <v>849</v>
+        <v>-9999</v>
       </c>
       <c r="H62" t="n">
-        <v>207</v>
+        <v>-9999</v>
       </c>
       <c r="I62" t="n">
-        <v>113</v>
+        <v>-9999</v>
       </c>
       <c r="J62" t="n">
-        <v>35.2</v>
+        <v>-9999</v>
       </c>
       <c r="K62" t="n">
-        <v>127</v>
+        <v>-9999</v>
       </c>
       <c r="L62" t="n">
-        <v>92</v>
+        <v>-9999</v>
       </c>
       <c r="M62" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N62" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="B63" t="s">
-        <v>33</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-9999</v>
+        <v>112</v>
+      </c>
+      <c r="C63" t="s">
+        <v>100</v>
       </c>
       <c r="D63" t="n">
         <v>-9999</v>
@@ -3208,18 +3753,21 @@
         <v>-9999</v>
       </c>
       <c r="M63" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N63" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="B64" t="s">
-        <v>33</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-9999</v>
+        <v>112</v>
+      </c>
+      <c r="C64" t="s">
+        <v>100</v>
       </c>
       <c r="D64" t="n">
         <v>-9999</v>
@@ -3249,18 +3797,21 @@
         <v>-9999</v>
       </c>
       <c r="M64" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N64" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="B65" t="s">
-        <v>33</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-9999</v>
+        <v>112</v>
+      </c>
+      <c r="C65" t="s">
+        <v>100</v>
       </c>
       <c r="D65" t="n">
         <v>-9999</v>
@@ -3290,18 +3841,21 @@
         <v>-9999</v>
       </c>
       <c r="M65" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N65" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="B66" t="s">
-        <v>33</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-9999</v>
+        <v>112</v>
+      </c>
+      <c r="C66" t="s">
+        <v>100</v>
       </c>
       <c r="D66" t="n">
         <v>-9999</v>
@@ -3331,18 +3885,21 @@
         <v>-9999</v>
       </c>
       <c r="M66" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N66" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="B67" t="s">
-        <v>101</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-9999</v>
+        <v>112</v>
+      </c>
+      <c r="C67" t="s">
+        <v>100</v>
       </c>
       <c r="D67" t="n">
         <v>-9999</v>
@@ -3372,18 +3929,21 @@
         <v>-9999</v>
       </c>
       <c r="M67" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N67" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="B68" t="s">
-        <v>101</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-9999</v>
+        <v>119</v>
+      </c>
+      <c r="C68" t="s">
+        <v>100</v>
       </c>
       <c r="D68" t="n">
         <v>-9999</v>
@@ -3413,18 +3973,21 @@
         <v>-9999</v>
       </c>
       <c r="M68" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N68" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="B69" t="s">
-        <v>101</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-9999</v>
+        <v>119</v>
+      </c>
+      <c r="C69" t="s">
+        <v>100</v>
       </c>
       <c r="D69" t="n">
         <v>-9999</v>
@@ -3454,18 +4017,21 @@
         <v>-9999</v>
       </c>
       <c r="M69" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N69" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="B70" t="s">
-        <v>101</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-9999</v>
+        <v>119</v>
+      </c>
+      <c r="C70" t="s">
+        <v>100</v>
       </c>
       <c r="D70" t="n">
         <v>-9999</v>
@@ -3495,18 +4061,21 @@
         <v>-9999</v>
       </c>
       <c r="M70" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N70" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="B71" t="s">
-        <v>101</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-9999</v>
+        <v>119</v>
+      </c>
+      <c r="C71" t="s">
+        <v>100</v>
       </c>
       <c r="D71" t="n">
         <v>-9999</v>
@@ -3536,18 +4105,21 @@
         <v>-9999</v>
       </c>
       <c r="M71" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N71" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="B72" t="s">
-        <v>101</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-9999</v>
+        <v>119</v>
+      </c>
+      <c r="C72" t="s">
+        <v>100</v>
       </c>
       <c r="D72" t="n">
         <v>-9999</v>
@@ -3577,18 +4149,21 @@
         <v>-9999</v>
       </c>
       <c r="M72" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N72" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="B73" t="s">
-        <v>108</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-9999</v>
+        <v>119</v>
+      </c>
+      <c r="C73" t="s">
+        <v>100</v>
       </c>
       <c r="D73" t="n">
         <v>-9999</v>
@@ -3618,18 +4193,21 @@
         <v>-9999</v>
       </c>
       <c r="M73" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N73" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="B74" t="s">
-        <v>108</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-9999</v>
+        <v>119</v>
+      </c>
+      <c r="C74" t="s">
+        <v>36</v>
       </c>
       <c r="D74" t="n">
         <v>-9999</v>
@@ -3659,18 +4237,21 @@
         <v>-9999</v>
       </c>
       <c r="M74" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N74" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="B75" t="s">
-        <v>108</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-9999</v>
+        <v>119</v>
+      </c>
+      <c r="C75" t="s">
+        <v>100</v>
       </c>
       <c r="D75" t="n">
         <v>-9999</v>
@@ -3700,18 +4281,21 @@
         <v>-9999</v>
       </c>
       <c r="M75" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N75" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B76" t="s">
-        <v>108</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-9999</v>
+        <v>119</v>
+      </c>
+      <c r="C76" t="s">
+        <v>100</v>
       </c>
       <c r="D76" t="n">
         <v>-9999</v>
@@ -3741,18 +4325,21 @@
         <v>-9999</v>
       </c>
       <c r="M76" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N76" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="B77" t="s">
-        <v>108</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-9999</v>
+        <v>129</v>
+      </c>
+      <c r="C77" t="s">
+        <v>100</v>
       </c>
       <c r="D77" t="n">
         <v>-9999</v>
@@ -3782,18 +4369,21 @@
         <v>-9999</v>
       </c>
       <c r="M77" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N77" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="B78" t="s">
-        <v>108</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-9999</v>
+        <v>129</v>
+      </c>
+      <c r="C78" t="s">
+        <v>100</v>
       </c>
       <c r="D78" t="n">
         <v>-9999</v>
@@ -3823,18 +4413,21 @@
         <v>-9999</v>
       </c>
       <c r="M78" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N78" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="B79" t="s">
-        <v>115</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-9999</v>
+        <v>129</v>
+      </c>
+      <c r="C79" t="s">
+        <v>100</v>
       </c>
       <c r="D79" t="n">
         <v>-9999</v>
@@ -3864,18 +4457,21 @@
         <v>-9999</v>
       </c>
       <c r="M79" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N79" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="B80" t="s">
-        <v>115</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-9999</v>
+        <v>129</v>
+      </c>
+      <c r="C80" t="s">
+        <v>100</v>
       </c>
       <c r="D80" t="n">
         <v>-9999</v>
@@ -3905,18 +4501,21 @@
         <v>-9999</v>
       </c>
       <c r="M80" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N80" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B81" t="s">
-        <v>115</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-9999</v>
+        <v>129</v>
+      </c>
+      <c r="C81" t="s">
+        <v>100</v>
       </c>
       <c r="D81" t="n">
         <v>-9999</v>
@@ -3946,18 +4545,21 @@
         <v>-9999</v>
       </c>
       <c r="M81" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N81" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="B82" t="s">
-        <v>115</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-9999</v>
+        <v>129</v>
+      </c>
+      <c r="C82" t="s">
+        <v>100</v>
       </c>
       <c r="D82" t="n">
         <v>-9999</v>
@@ -3987,18 +4589,21 @@
         <v>-9999</v>
       </c>
       <c r="M82" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N82" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="B83" t="s">
-        <v>115</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-9999</v>
+        <v>129</v>
+      </c>
+      <c r="C83" t="s">
+        <v>100</v>
       </c>
       <c r="D83" t="n">
         <v>-9999</v>
@@ -4028,18 +4633,21 @@
         <v>-9999</v>
       </c>
       <c r="M83" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N83" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="B84" t="s">
-        <v>115</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-9999</v>
+        <v>129</v>
+      </c>
+      <c r="C84" t="s">
+        <v>100</v>
       </c>
       <c r="D84" t="n">
         <v>-9999</v>
@@ -4069,18 +4677,21 @@
         <v>-9999</v>
       </c>
       <c r="M84" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N84" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="B85" t="s">
-        <v>115</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-9999</v>
+        <v>129</v>
+      </c>
+      <c r="C85" t="s">
+        <v>100</v>
       </c>
       <c r="D85" t="n">
         <v>-9999</v>
@@ -4110,18 +4721,21 @@
         <v>-9999</v>
       </c>
       <c r="M85" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N85" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B86" t="s">
-        <v>115</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-9999</v>
+        <v>129</v>
+      </c>
+      <c r="C86" t="s">
+        <v>100</v>
       </c>
       <c r="D86" t="n">
         <v>-9999</v>
@@ -4151,18 +4765,21 @@
         <v>-9999</v>
       </c>
       <c r="M86" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N86" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B87" t="s">
-        <v>115</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-9999</v>
+        <v>129</v>
+      </c>
+      <c r="C87" t="s">
+        <v>100</v>
       </c>
       <c r="D87" t="n">
         <v>-9999</v>
@@ -4192,18 +4809,21 @@
         <v>-9999</v>
       </c>
       <c r="M87" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N87" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="B88" t="s">
-        <v>125</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-9999</v>
+        <v>141</v>
+      </c>
+      <c r="C88" t="s">
+        <v>100</v>
       </c>
       <c r="D88" t="n">
         <v>-9999</v>
@@ -4233,18 +4853,21 @@
         <v>-9999</v>
       </c>
       <c r="M88" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N88" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B89" t="s">
-        <v>125</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-9999</v>
+        <v>141</v>
+      </c>
+      <c r="C89" t="s">
+        <v>100</v>
       </c>
       <c r="D89" t="n">
         <v>-9999</v>
@@ -4274,18 +4897,21 @@
         <v>-9999</v>
       </c>
       <c r="M89" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N89" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B90" t="s">
-        <v>125</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-9999</v>
+        <v>141</v>
+      </c>
+      <c r="C90" t="s">
+        <v>100</v>
       </c>
       <c r="D90" t="n">
         <v>-9999</v>
@@ -4315,18 +4941,21 @@
         <v>-9999</v>
       </c>
       <c r="M90" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N90" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="B91" t="s">
-        <v>125</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-9999</v>
+        <v>141</v>
+      </c>
+      <c r="C91" t="s">
+        <v>100</v>
       </c>
       <c r="D91" t="n">
         <v>-9999</v>
@@ -4356,18 +4985,21 @@
         <v>-9999</v>
       </c>
       <c r="M91" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N91" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="B92" t="s">
-        <v>125</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-9999</v>
+        <v>141</v>
+      </c>
+      <c r="C92" t="s">
+        <v>100</v>
       </c>
       <c r="D92" t="n">
         <v>-9999</v>
@@ -4397,18 +5029,21 @@
         <v>-9999</v>
       </c>
       <c r="M92" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N92" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="B93" t="s">
-        <v>125</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-9999</v>
+        <v>141</v>
+      </c>
+      <c r="C93" t="s">
+        <v>100</v>
       </c>
       <c r="D93" t="n">
         <v>-9999</v>
@@ -4438,18 +5073,21 @@
         <v>-9999</v>
       </c>
       <c r="M93" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N93" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="B94" t="s">
-        <v>125</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-9999</v>
+        <v>141</v>
+      </c>
+      <c r="C94" t="s">
+        <v>100</v>
       </c>
       <c r="D94" t="n">
         <v>-9999</v>
@@ -4479,18 +5117,21 @@
         <v>-9999</v>
       </c>
       <c r="M94" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N94" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="B95" t="s">
-        <v>125</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-9999</v>
+        <v>141</v>
+      </c>
+      <c r="C95" t="s">
+        <v>100</v>
       </c>
       <c r="D95" t="n">
         <v>-9999</v>
@@ -4520,18 +5161,21 @@
         <v>-9999</v>
       </c>
       <c r="M95" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N95" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B96" t="s">
-        <v>125</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-9999</v>
+        <v>141</v>
+      </c>
+      <c r="C96" t="s">
+        <v>100</v>
       </c>
       <c r="D96" t="n">
         <v>-9999</v>
@@ -4561,18 +5205,21 @@
         <v>-9999</v>
       </c>
       <c r="M96" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N96" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="B97" t="s">
-        <v>125</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-9999</v>
+        <v>86</v>
+      </c>
+      <c r="C97" t="s">
+        <v>100</v>
       </c>
       <c r="D97" t="n">
         <v>-9999</v>
@@ -4602,18 +5249,21 @@
         <v>-9999</v>
       </c>
       <c r="M97" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N97" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B98" t="s">
-        <v>125</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-9999</v>
+        <v>86</v>
+      </c>
+      <c r="C98" t="s">
+        <v>100</v>
       </c>
       <c r="D98" t="n">
         <v>-9999</v>
@@ -4643,18 +5293,21 @@
         <v>-9999</v>
       </c>
       <c r="M98" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N98" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="B99" t="s">
-        <v>137</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-9999</v>
+        <v>86</v>
+      </c>
+      <c r="C99" t="s">
+        <v>100</v>
       </c>
       <c r="D99" t="n">
         <v>-9999</v>
@@ -4684,18 +5337,21 @@
         <v>-9999</v>
       </c>
       <c r="M99" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N99" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="B100" t="s">
-        <v>137</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-9999</v>
+        <v>86</v>
+      </c>
+      <c r="C100" t="s">
+        <v>100</v>
       </c>
       <c r="D100" t="n">
         <v>-9999</v>
@@ -4725,18 +5381,21 @@
         <v>-9999</v>
       </c>
       <c r="M100" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N100" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="B101" t="s">
-        <v>137</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-9999</v>
+        <v>86</v>
+      </c>
+      <c r="C101" t="s">
+        <v>100</v>
       </c>
       <c r="D101" t="n">
         <v>-9999</v>
@@ -4766,18 +5425,21 @@
         <v>-9999</v>
       </c>
       <c r="M101" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N101" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="B102" t="s">
-        <v>137</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-9999</v>
+        <v>86</v>
+      </c>
+      <c r="C102" t="s">
+        <v>36</v>
       </c>
       <c r="D102" t="n">
         <v>-9999</v>
@@ -4807,18 +5469,21 @@
         <v>-9999</v>
       </c>
       <c r="M102" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N102" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="B103" t="s">
-        <v>137</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-9999</v>
+        <v>86</v>
+      </c>
+      <c r="C103" t="s">
+        <v>100</v>
       </c>
       <c r="D103" t="n">
         <v>-9999</v>
@@ -4848,18 +5513,21 @@
         <v>-9999</v>
       </c>
       <c r="M103" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N103" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="B104" t="s">
-        <v>137</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-9999</v>
+        <v>86</v>
+      </c>
+      <c r="C104" t="s">
+        <v>100</v>
       </c>
       <c r="D104" t="n">
         <v>-9999</v>
@@ -4889,18 +5557,21 @@
         <v>-9999</v>
       </c>
       <c r="M104" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N104" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="B105" t="s">
-        <v>137</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-9999</v>
+        <v>159</v>
+      </c>
+      <c r="C105" t="s">
+        <v>100</v>
       </c>
       <c r="D105" t="n">
         <v>-9999</v>
@@ -4930,18 +5601,21 @@
         <v>-9999</v>
       </c>
       <c r="M105" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N105" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="B106" t="s">
-        <v>137</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-9999</v>
+        <v>159</v>
+      </c>
+      <c r="C106" t="s">
+        <v>100</v>
       </c>
       <c r="D106" t="n">
         <v>-9999</v>
@@ -4971,18 +5645,21 @@
         <v>-9999</v>
       </c>
       <c r="M106" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N106" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="B107" t="s">
-        <v>137</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-9999</v>
+        <v>159</v>
+      </c>
+      <c r="C107" t="s">
+        <v>100</v>
       </c>
       <c r="D107" t="n">
         <v>-9999</v>
@@ -5012,18 +5689,21 @@
         <v>-9999</v>
       </c>
       <c r="M107" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N107" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="B108" t="s">
-        <v>83</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-9999</v>
+        <v>159</v>
+      </c>
+      <c r="C108" t="s">
+        <v>100</v>
       </c>
       <c r="D108" t="n">
         <v>-9999</v>
@@ -5053,18 +5733,21 @@
         <v>-9999</v>
       </c>
       <c r="M108" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N108" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="B109" t="s">
-        <v>83</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-9999</v>
+        <v>159</v>
+      </c>
+      <c r="C109" t="s">
+        <v>100</v>
       </c>
       <c r="D109" t="n">
         <v>-9999</v>
@@ -5094,18 +5777,21 @@
         <v>-9999</v>
       </c>
       <c r="M109" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N109" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="B110" t="s">
-        <v>83</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-9999</v>
+        <v>159</v>
+      </c>
+      <c r="C110" t="s">
+        <v>100</v>
       </c>
       <c r="D110" t="n">
         <v>-9999</v>
@@ -5135,18 +5821,21 @@
         <v>-9999</v>
       </c>
       <c r="M110" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N110" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="B111" t="s">
-        <v>83</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-9999</v>
+        <v>159</v>
+      </c>
+      <c r="C111" t="s">
+        <v>36</v>
       </c>
       <c r="D111" t="n">
         <v>-9999</v>
@@ -5176,18 +5865,21 @@
         <v>-9999</v>
       </c>
       <c r="M111" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N111" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="B112" t="s">
-        <v>83</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-9999</v>
+        <v>159</v>
+      </c>
+      <c r="C112" t="s">
+        <v>100</v>
       </c>
       <c r="D112" t="n">
         <v>-9999</v>
@@ -5217,18 +5909,21 @@
         <v>-9999</v>
       </c>
       <c r="M112" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N112" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="B113" t="s">
-        <v>83</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-9999</v>
+        <v>159</v>
+      </c>
+      <c r="C113" t="s">
+        <v>100</v>
       </c>
       <c r="D113" t="n">
         <v>-9999</v>
@@ -5258,18 +5953,21 @@
         <v>-9999</v>
       </c>
       <c r="M113" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N113" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="B114" t="s">
-        <v>83</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-9999</v>
+        <v>169</v>
+      </c>
+      <c r="C114" t="s">
+        <v>100</v>
       </c>
       <c r="D114" t="n">
         <v>-9999</v>
@@ -5299,18 +5997,21 @@
         <v>-9999</v>
       </c>
       <c r="M114" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N114" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="B115" t="s">
-        <v>83</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-9999</v>
+        <v>169</v>
+      </c>
+      <c r="C115" t="s">
+        <v>100</v>
       </c>
       <c r="D115" t="n">
         <v>-9999</v>
@@ -5340,18 +6041,21 @@
         <v>-9999</v>
       </c>
       <c r="M115" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N115" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="B116" t="s">
-        <v>155</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-9999</v>
+        <v>169</v>
+      </c>
+      <c r="C116" t="s">
+        <v>100</v>
       </c>
       <c r="D116" t="n">
         <v>-9999</v>
@@ -5381,18 +6085,21 @@
         <v>-9999</v>
       </c>
       <c r="M116" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N116" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="B117" t="s">
-        <v>155</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-9999</v>
+        <v>169</v>
+      </c>
+      <c r="C117" t="s">
+        <v>100</v>
       </c>
       <c r="D117" t="n">
         <v>-9999</v>
@@ -5422,18 +6129,21 @@
         <v>-9999</v>
       </c>
       <c r="M117" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N117" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="B118" t="s">
-        <v>155</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-9999</v>
+        <v>169</v>
+      </c>
+      <c r="C118" t="s">
+        <v>100</v>
       </c>
       <c r="D118" t="n">
         <v>-9999</v>
@@ -5463,18 +6173,21 @@
         <v>-9999</v>
       </c>
       <c r="M118" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N118" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B119" t="s">
-        <v>155</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-9999</v>
+        <v>169</v>
+      </c>
+      <c r="C119" t="s">
+        <v>100</v>
       </c>
       <c r="D119" t="n">
         <v>-9999</v>
@@ -5504,18 +6217,21 @@
         <v>-9999</v>
       </c>
       <c r="M119" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N119" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="B120" t="s">
-        <v>155</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-9999</v>
+        <v>169</v>
+      </c>
+      <c r="C120" t="s">
+        <v>100</v>
       </c>
       <c r="D120" t="n">
         <v>-9999</v>
@@ -5545,18 +6261,21 @@
         <v>-9999</v>
       </c>
       <c r="M120" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N120" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="B121" t="s">
-        <v>155</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-9999</v>
+        <v>169</v>
+      </c>
+      <c r="C121" t="s">
+        <v>100</v>
       </c>
       <c r="D121" t="n">
         <v>-9999</v>
@@ -5586,18 +6305,21 @@
         <v>-9999</v>
       </c>
       <c r="M121" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N121" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="B122" t="s">
-        <v>155</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-9999</v>
+        <v>169</v>
+      </c>
+      <c r="C122" t="s">
+        <v>100</v>
       </c>
       <c r="D122" t="n">
         <v>-9999</v>
@@ -5627,18 +6349,21 @@
         <v>-9999</v>
       </c>
       <c r="M122" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N122" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="B123" t="s">
-        <v>155</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-9999</v>
+        <v>70</v>
+      </c>
+      <c r="C123" t="s">
+        <v>23</v>
       </c>
       <c r="D123" t="n">
         <v>-9999</v>
@@ -5668,18 +6393,21 @@
         <v>-9999</v>
       </c>
       <c r="M123" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N123" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="B124" t="s">
-        <v>155</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-9999</v>
+        <v>42</v>
+      </c>
+      <c r="C124" t="s">
+        <v>100</v>
       </c>
       <c r="D124" t="n">
         <v>-9999</v>
@@ -5709,18 +6437,21 @@
         <v>-9999</v>
       </c>
       <c r="M124" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N124" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="B125" t="s">
-        <v>165</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-9999</v>
+        <v>42</v>
+      </c>
+      <c r="C125" t="s">
+        <v>100</v>
       </c>
       <c r="D125" t="n">
         <v>-9999</v>
@@ -5750,18 +6481,21 @@
         <v>-9999</v>
       </c>
       <c r="M125" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N125" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B126" t="s">
-        <v>165</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-9999</v>
+        <v>42</v>
+      </c>
+      <c r="C126" t="s">
+        <v>100</v>
       </c>
       <c r="D126" t="n">
         <v>-9999</v>
@@ -5791,18 +6525,21 @@
         <v>-9999</v>
       </c>
       <c r="M126" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N126" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="B127" t="s">
-        <v>165</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-9999</v>
+        <v>42</v>
+      </c>
+      <c r="C127" t="s">
+        <v>100</v>
       </c>
       <c r="D127" t="n">
         <v>-9999</v>
@@ -5832,18 +6569,21 @@
         <v>-9999</v>
       </c>
       <c r="M127" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N127" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="B128" t="s">
-        <v>165</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-9999</v>
+        <v>42</v>
+      </c>
+      <c r="C128" t="s">
+        <v>100</v>
       </c>
       <c r="D128" t="n">
         <v>-9999</v>
@@ -5873,18 +6613,21 @@
         <v>-9999</v>
       </c>
       <c r="M128" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N128" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="B129" t="s">
-        <v>165</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-9999</v>
+        <v>42</v>
+      </c>
+      <c r="C129" t="s">
+        <v>100</v>
       </c>
       <c r="D129" t="n">
         <v>-9999</v>
@@ -5914,18 +6657,21 @@
         <v>-9999</v>
       </c>
       <c r="M129" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N129" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="B130" t="s">
-        <v>165</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-9999</v>
+        <v>42</v>
+      </c>
+      <c r="C130" t="s">
+        <v>100</v>
       </c>
       <c r="D130" t="n">
         <v>-9999</v>
@@ -5955,18 +6701,21 @@
         <v>-9999</v>
       </c>
       <c r="M130" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N130" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="B131" t="s">
-        <v>165</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-9999</v>
+        <v>40</v>
+      </c>
+      <c r="C131" t="s">
+        <v>100</v>
       </c>
       <c r="D131" t="n">
         <v>-9999</v>
@@ -5996,18 +6745,21 @@
         <v>-9999</v>
       </c>
       <c r="M131" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N131" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="B132" t="s">
-        <v>165</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-9999</v>
+        <v>40</v>
+      </c>
+      <c r="C132" t="s">
+        <v>100</v>
       </c>
       <c r="D132" t="n">
         <v>-9999</v>
@@ -6037,18 +6789,21 @@
         <v>-9999</v>
       </c>
       <c r="M132" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N132" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="B133" t="s">
-        <v>165</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-9999</v>
+        <v>189</v>
+      </c>
+      <c r="C133" t="s">
+        <v>100</v>
       </c>
       <c r="D133" t="n">
         <v>-9999</v>
@@ -6078,18 +6833,21 @@
         <v>-9999</v>
       </c>
       <c r="M133" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N133" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="B134" t="s">
-        <v>67</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-9999</v>
+        <v>189</v>
+      </c>
+      <c r="C134" t="s">
+        <v>100</v>
       </c>
       <c r="D134" t="n">
         <v>-9999</v>
@@ -6119,18 +6877,21 @@
         <v>-9999</v>
       </c>
       <c r="M134" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N134" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="B135" t="s">
-        <v>39</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-9999</v>
+        <v>189</v>
+      </c>
+      <c r="C135" t="s">
+        <v>100</v>
       </c>
       <c r="D135" t="n">
         <v>-9999</v>
@@ -6160,18 +6921,21 @@
         <v>-9999</v>
       </c>
       <c r="M135" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N135" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="B136" t="s">
-        <v>39</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-9999</v>
+        <v>189</v>
+      </c>
+      <c r="C136" t="s">
+        <v>100</v>
       </c>
       <c r="D136" t="n">
         <v>-9999</v>
@@ -6201,18 +6965,21 @@
         <v>-9999</v>
       </c>
       <c r="M136" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N136" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="B137" t="s">
-        <v>39</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-9999</v>
+        <v>189</v>
+      </c>
+      <c r="C137" t="s">
+        <v>100</v>
       </c>
       <c r="D137" t="n">
         <v>-9999</v>
@@ -6242,18 +7009,21 @@
         <v>-9999</v>
       </c>
       <c r="M137" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N137" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="B138" t="s">
-        <v>39</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-9999</v>
+        <v>189</v>
+      </c>
+      <c r="C138" t="s">
+        <v>100</v>
       </c>
       <c r="D138" t="n">
         <v>-9999</v>
@@ -6283,18 +7053,21 @@
         <v>-9999</v>
       </c>
       <c r="M138" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N138" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="B139" t="s">
-        <v>39</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-9999</v>
+        <v>38</v>
+      </c>
+      <c r="C139" t="s">
+        <v>100</v>
       </c>
       <c r="D139" t="n">
         <v>-9999</v>
@@ -6324,18 +7097,21 @@
         <v>-9999</v>
       </c>
       <c r="M139" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N139" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="B140" t="s">
-        <v>39</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-9999</v>
+        <v>38</v>
+      </c>
+      <c r="C140" t="s">
+        <v>100</v>
       </c>
       <c r="D140" t="n">
         <v>-9999</v>
@@ -6365,18 +7141,21 @@
         <v>-9999</v>
       </c>
       <c r="M140" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N140" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="B141" t="s">
-        <v>39</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-9999</v>
+        <v>38</v>
+      </c>
+      <c r="C141" t="s">
+        <v>100</v>
       </c>
       <c r="D141" t="n">
         <v>-9999</v>
@@ -6406,18 +7185,21 @@
         <v>-9999</v>
       </c>
       <c r="M141" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N141" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="B142" t="s">
-        <v>37</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-9999</v>
+        <v>38</v>
+      </c>
+      <c r="C142" t="s">
+        <v>100</v>
       </c>
       <c r="D142" t="n">
         <v>-9999</v>
@@ -6447,18 +7229,21 @@
         <v>-9999</v>
       </c>
       <c r="M142" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N142" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="B143" t="s">
-        <v>37</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-9999</v>
+        <v>38</v>
+      </c>
+      <c r="C143" t="s">
+        <v>100</v>
       </c>
       <c r="D143" t="n">
         <v>-9999</v>
@@ -6488,18 +7273,21 @@
         <v>-9999</v>
       </c>
       <c r="M143" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N143" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="B144" t="s">
-        <v>185</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-9999</v>
+        <v>38</v>
+      </c>
+      <c r="C144" t="s">
+        <v>100</v>
       </c>
       <c r="D144" t="n">
         <v>-9999</v>
@@ -6529,18 +7317,21 @@
         <v>-9999</v>
       </c>
       <c r="M144" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N144" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="B145" t="s">
-        <v>185</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-9999</v>
+        <v>38</v>
+      </c>
+      <c r="C145" t="s">
+        <v>100</v>
       </c>
       <c r="D145" t="n">
         <v>-9999</v>
@@ -6570,18 +7361,21 @@
         <v>-9999</v>
       </c>
       <c r="M145" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N145" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="B146" t="s">
-        <v>185</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-9999</v>
+        <v>203</v>
+      </c>
+      <c r="C146" t="s">
+        <v>36</v>
       </c>
       <c r="D146" t="n">
         <v>-9999</v>
@@ -6611,18 +7405,21 @@
         <v>-9999</v>
       </c>
       <c r="M146" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N146" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="B147" t="s">
-        <v>185</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-9999</v>
+        <v>203</v>
+      </c>
+      <c r="C147" t="s">
+        <v>100</v>
       </c>
       <c r="D147" t="n">
         <v>-9999</v>
@@ -6652,18 +7449,21 @@
         <v>-9999</v>
       </c>
       <c r="M147" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N147" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="B148" t="s">
-        <v>185</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-9999</v>
+        <v>206</v>
+      </c>
+      <c r="C148" t="s">
+        <v>100</v>
       </c>
       <c r="D148" t="n">
         <v>-9999</v>
@@ -6693,18 +7493,21 @@
         <v>-9999</v>
       </c>
       <c r="M148" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N148" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="B149" t="s">
-        <v>185</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-9999</v>
+        <v>206</v>
+      </c>
+      <c r="C149" t="s">
+        <v>100</v>
       </c>
       <c r="D149" t="n">
         <v>-9999</v>
@@ -6734,18 +7537,21 @@
         <v>-9999</v>
       </c>
       <c r="M149" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N149" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="B150" t="s">
-        <v>35</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-9999</v>
+        <v>206</v>
+      </c>
+      <c r="C150" t="s">
+        <v>100</v>
       </c>
       <c r="D150" t="n">
         <v>-9999</v>
@@ -6775,18 +7581,21 @@
         <v>-9999</v>
       </c>
       <c r="M150" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N150" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="B151" t="s">
-        <v>35</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-9999</v>
+        <v>206</v>
+      </c>
+      <c r="C151" t="s">
+        <v>100</v>
       </c>
       <c r="D151" t="n">
         <v>-9999</v>
@@ -6816,18 +7625,21 @@
         <v>-9999</v>
       </c>
       <c r="M151" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N151" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="B152" t="s">
-        <v>35</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-9999</v>
+        <v>206</v>
+      </c>
+      <c r="C152" t="s">
+        <v>100</v>
       </c>
       <c r="D152" t="n">
         <v>-9999</v>
@@ -6857,18 +7669,21 @@
         <v>-9999</v>
       </c>
       <c r="M152" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N152" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="B153" t="s">
-        <v>35</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-9999</v>
+        <v>206</v>
+      </c>
+      <c r="C153" t="s">
+        <v>100</v>
       </c>
       <c r="D153" t="n">
         <v>-9999</v>
@@ -6898,18 +7713,21 @@
         <v>-9999</v>
       </c>
       <c r="M153" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N153" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="B154" t="s">
-        <v>35</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-9999</v>
+        <v>206</v>
+      </c>
+      <c r="C154" t="s">
+        <v>100</v>
       </c>
       <c r="D154" t="n">
         <v>-9999</v>
@@ -6939,18 +7757,21 @@
         <v>-9999</v>
       </c>
       <c r="M154" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N154" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="B155" t="s">
-        <v>35</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-9999</v>
+        <v>206</v>
+      </c>
+      <c r="C155" t="s">
+        <v>100</v>
       </c>
       <c r="D155" t="n">
         <v>-9999</v>
@@ -6980,18 +7801,21 @@
         <v>-9999</v>
       </c>
       <c r="M155" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N155" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="B156" t="s">
-        <v>35</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-9999</v>
+        <v>206</v>
+      </c>
+      <c r="C156" t="s">
+        <v>100</v>
       </c>
       <c r="D156" t="n">
         <v>-9999</v>
@@ -7021,18 +7845,21 @@
         <v>-9999</v>
       </c>
       <c r="M156" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N156" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="B157" t="s">
-        <v>199</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-9999</v>
+        <v>206</v>
+      </c>
+      <c r="C157" t="s">
+        <v>100</v>
       </c>
       <c r="D157" t="n">
         <v>-9999</v>
@@ -7062,18 +7889,21 @@
         <v>-9999</v>
       </c>
       <c r="M157" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N157" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="B158" t="s">
-        <v>199</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-9999</v>
+        <v>217</v>
+      </c>
+      <c r="C158" t="s">
+        <v>100</v>
       </c>
       <c r="D158" t="n">
         <v>-9999</v>
@@ -7103,18 +7933,21 @@
         <v>-9999</v>
       </c>
       <c r="M158" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N158" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="B159" t="s">
-        <v>202</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-9999</v>
+        <v>217</v>
+      </c>
+      <c r="C159" t="s">
+        <v>100</v>
       </c>
       <c r="D159" t="n">
         <v>-9999</v>
@@ -7144,18 +7977,21 @@
         <v>-9999</v>
       </c>
       <c r="M159" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N159" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="B160" t="s">
-        <v>202</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-9999</v>
+        <v>217</v>
+      </c>
+      <c r="C160" t="s">
+        <v>100</v>
       </c>
       <c r="D160" t="n">
         <v>-9999</v>
@@ -7185,18 +8021,21 @@
         <v>-9999</v>
       </c>
       <c r="M160" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N160" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="B161" t="s">
-        <v>202</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-9999</v>
+        <v>217</v>
+      </c>
+      <c r="C161" t="s">
+        <v>100</v>
       </c>
       <c r="D161" t="n">
         <v>-9999</v>
@@ -7226,18 +8065,21 @@
         <v>-9999</v>
       </c>
       <c r="M161" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N161" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="B162" t="s">
-        <v>202</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-9999</v>
+        <v>217</v>
+      </c>
+      <c r="C162" t="s">
+        <v>100</v>
       </c>
       <c r="D162" t="n">
         <v>-9999</v>
@@ -7267,18 +8109,21 @@
         <v>-9999</v>
       </c>
       <c r="M162" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N162" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="B163" t="s">
-        <v>202</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-9999</v>
+        <v>217</v>
+      </c>
+      <c r="C163" t="s">
+        <v>100</v>
       </c>
       <c r="D163" t="n">
         <v>-9999</v>
@@ -7308,18 +8153,21 @@
         <v>-9999</v>
       </c>
       <c r="M163" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N163" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B164" t="s">
-        <v>202</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-9999</v>
+        <v>217</v>
+      </c>
+      <c r="C164" t="s">
+        <v>100</v>
       </c>
       <c r="D164" t="n">
         <v>-9999</v>
@@ -7349,18 +8197,21 @@
         <v>-9999</v>
       </c>
       <c r="M164" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N164" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="B165" t="s">
-        <v>202</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-9999</v>
+        <v>217</v>
+      </c>
+      <c r="C165" t="s">
+        <v>100</v>
       </c>
       <c r="D165" t="n">
         <v>-9999</v>
@@ -7390,18 +8241,21 @@
         <v>-9999</v>
       </c>
       <c r="M165" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N165" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="B166" t="s">
-        <v>202</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-9999</v>
+        <v>217</v>
+      </c>
+      <c r="C166" t="s">
+        <v>100</v>
       </c>
       <c r="D166" t="n">
         <v>-9999</v>
@@ -7431,18 +8285,21 @@
         <v>-9999</v>
       </c>
       <c r="M166" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N166" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="B167" t="s">
-        <v>202</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-9999</v>
+        <v>217</v>
+      </c>
+      <c r="C167" t="s">
+        <v>100</v>
       </c>
       <c r="D167" t="n">
         <v>-9999</v>
@@ -7472,18 +8329,21 @@
         <v>-9999</v>
       </c>
       <c r="M167" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N167" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B168" t="s">
-        <v>202</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-9999</v>
+        <v>217</v>
+      </c>
+      <c r="C168" t="s">
+        <v>100</v>
       </c>
       <c r="D168" t="n">
         <v>-9999</v>
@@ -7513,18 +8373,21 @@
         <v>-9999</v>
       </c>
       <c r="M168" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N168" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="B169" t="s">
-        <v>213</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-9999</v>
+        <v>229</v>
+      </c>
+      <c r="C169" t="s">
+        <v>100</v>
       </c>
       <c r="D169" t="n">
         <v>-9999</v>
@@ -7554,18 +8417,21 @@
         <v>-9999</v>
       </c>
       <c r="M169" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N169" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="B170" t="s">
-        <v>213</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-9999</v>
+        <v>229</v>
+      </c>
+      <c r="C170" t="s">
+        <v>100</v>
       </c>
       <c r="D170" t="n">
         <v>-9999</v>
@@ -7595,18 +8461,21 @@
         <v>-9999</v>
       </c>
       <c r="M170" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N170" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="B171" t="s">
-        <v>213</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-9999</v>
+        <v>229</v>
+      </c>
+      <c r="C171" t="s">
+        <v>100</v>
       </c>
       <c r="D171" t="n">
         <v>-9999</v>
@@ -7636,18 +8505,21 @@
         <v>-9999</v>
       </c>
       <c r="M171" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N171" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="B172" t="s">
-        <v>213</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-9999</v>
+        <v>229</v>
+      </c>
+      <c r="C172" t="s">
+        <v>100</v>
       </c>
       <c r="D172" t="n">
         <v>-9999</v>
@@ -7677,18 +8549,21 @@
         <v>-9999</v>
       </c>
       <c r="M172" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N172" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="B173" t="s">
-        <v>213</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-9999</v>
+        <v>229</v>
+      </c>
+      <c r="C173" t="s">
+        <v>100</v>
       </c>
       <c r="D173" t="n">
         <v>-9999</v>
@@ -7718,18 +8593,21 @@
         <v>-9999</v>
       </c>
       <c r="M173" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N173" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="B174" t="s">
-        <v>213</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-9999</v>
+        <v>229</v>
+      </c>
+      <c r="C174" t="s">
+        <v>100</v>
       </c>
       <c r="D174" t="n">
         <v>-9999</v>
@@ -7759,18 +8637,21 @@
         <v>-9999</v>
       </c>
       <c r="M174" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N174" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="B175" t="s">
-        <v>213</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-9999</v>
+        <v>229</v>
+      </c>
+      <c r="C175" t="s">
+        <v>100</v>
       </c>
       <c r="D175" t="n">
         <v>-9999</v>
@@ -7800,18 +8681,21 @@
         <v>-9999</v>
       </c>
       <c r="M175" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N175" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="B176" t="s">
-        <v>213</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-9999</v>
+        <v>237</v>
+      </c>
+      <c r="C176" t="s">
+        <v>100</v>
       </c>
       <c r="D176" t="n">
         <v>-9999</v>
@@ -7841,18 +8725,21 @@
         <v>-9999</v>
       </c>
       <c r="M176" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N176" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="B177" t="s">
-        <v>213</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-9999</v>
+        <v>237</v>
+      </c>
+      <c r="C177" t="s">
+        <v>100</v>
       </c>
       <c r="D177" t="n">
         <v>-9999</v>
@@ -7882,18 +8769,21 @@
         <v>-9999</v>
       </c>
       <c r="M177" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N177" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="B178" t="s">
-        <v>213</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-9999</v>
+        <v>237</v>
+      </c>
+      <c r="C178" t="s">
+        <v>100</v>
       </c>
       <c r="D178" t="n">
         <v>-9999</v>
@@ -7923,18 +8813,21 @@
         <v>-9999</v>
       </c>
       <c r="M178" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N178" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="B179" t="s">
-        <v>213</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-9999</v>
+        <v>237</v>
+      </c>
+      <c r="C179" t="s">
+        <v>100</v>
       </c>
       <c r="D179" t="n">
         <v>-9999</v>
@@ -7964,18 +8857,21 @@
         <v>-9999</v>
       </c>
       <c r="M179" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N179" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="B180" t="s">
-        <v>225</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-9999</v>
+        <v>237</v>
+      </c>
+      <c r="C180" t="s">
+        <v>100</v>
       </c>
       <c r="D180" t="n">
         <v>-9999</v>
@@ -8005,18 +8901,21 @@
         <v>-9999</v>
       </c>
       <c r="M180" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N180" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B181" t="s">
-        <v>225</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-9999</v>
+        <v>237</v>
+      </c>
+      <c r="C181" t="s">
+        <v>100</v>
       </c>
       <c r="D181" t="n">
         <v>-9999</v>
@@ -8046,18 +8945,21 @@
         <v>-9999</v>
       </c>
       <c r="M181" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N181" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="B182" t="s">
-        <v>225</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-9999</v>
+        <v>237</v>
+      </c>
+      <c r="C182" t="s">
+        <v>100</v>
       </c>
       <c r="D182" t="n">
         <v>-9999</v>
@@ -8087,18 +8989,21 @@
         <v>-9999</v>
       </c>
       <c r="M182" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N182" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="B183" t="s">
-        <v>225</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-9999</v>
+        <v>237</v>
+      </c>
+      <c r="C183" t="s">
+        <v>100</v>
       </c>
       <c r="D183" t="n">
         <v>-9999</v>
@@ -8128,18 +9033,21 @@
         <v>-9999</v>
       </c>
       <c r="M183" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N183" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B184" t="s">
-        <v>225</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-9999</v>
+        <v>237</v>
+      </c>
+      <c r="C184" t="s">
+        <v>100</v>
       </c>
       <c r="D184" t="n">
         <v>-9999</v>
@@ -8169,18 +9077,21 @@
         <v>-9999</v>
       </c>
       <c r="M184" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N184" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="B185" t="s">
-        <v>225</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-9999</v>
+        <v>237</v>
+      </c>
+      <c r="C185" t="s">
+        <v>100</v>
       </c>
       <c r="D185" t="n">
         <v>-9999</v>
@@ -8210,18 +9121,21 @@
         <v>-9999</v>
       </c>
       <c r="M185" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N185" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="B186" t="s">
-        <v>225</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-9999</v>
+        <v>46</v>
+      </c>
+      <c r="C186" t="s">
+        <v>100</v>
       </c>
       <c r="D186" t="n">
         <v>-9999</v>
@@ -8251,18 +9165,21 @@
         <v>-9999</v>
       </c>
       <c r="M186" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N186" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="B187" t="s">
-        <v>233</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-9999</v>
+        <v>249</v>
+      </c>
+      <c r="C187" t="s">
+        <v>100</v>
       </c>
       <c r="D187" t="n">
         <v>-9999</v>
@@ -8292,18 +9209,21 @@
         <v>-9999</v>
       </c>
       <c r="M187" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N187" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="B188" t="s">
-        <v>233</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-9999</v>
+        <v>249</v>
+      </c>
+      <c r="C188" t="s">
+        <v>100</v>
       </c>
       <c r="D188" t="n">
         <v>-9999</v>
@@ -8333,18 +9253,21 @@
         <v>-9999</v>
       </c>
       <c r="M188" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N188" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="B189" t="s">
-        <v>233</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-9999</v>
+        <v>249</v>
+      </c>
+      <c r="C189" t="s">
+        <v>100</v>
       </c>
       <c r="D189" t="n">
         <v>-9999</v>
@@ -8374,18 +9297,21 @@
         <v>-9999</v>
       </c>
       <c r="M189" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N189" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="B190" t="s">
-        <v>233</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-9999</v>
+        <v>249</v>
+      </c>
+      <c r="C190" t="s">
+        <v>100</v>
       </c>
       <c r="D190" t="n">
         <v>-9999</v>
@@ -8415,18 +9341,21 @@
         <v>-9999</v>
       </c>
       <c r="M190" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N190" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="B191" t="s">
-        <v>233</v>
-      </c>
-      <c r="C191" t="n">
-        <v>-9999</v>
+        <v>249</v>
+      </c>
+      <c r="C191" t="s">
+        <v>100</v>
       </c>
       <c r="D191" t="n">
         <v>-9999</v>
@@ -8456,18 +9385,21 @@
         <v>-9999</v>
       </c>
       <c r="M191" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N191" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B192" t="s">
-        <v>233</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-9999</v>
+        <v>249</v>
+      </c>
+      <c r="C192" t="s">
+        <v>100</v>
       </c>
       <c r="D192" t="n">
         <v>-9999</v>
@@ -8497,18 +9429,21 @@
         <v>-9999</v>
       </c>
       <c r="M192" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N192" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="B193" t="s">
-        <v>233</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-9999</v>
+        <v>249</v>
+      </c>
+      <c r="C193" t="s">
+        <v>100</v>
       </c>
       <c r="D193" t="n">
         <v>-9999</v>
@@ -8538,18 +9473,21 @@
         <v>-9999</v>
       </c>
       <c r="M193" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N193" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="B194" t="s">
-        <v>233</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-9999</v>
+        <v>249</v>
+      </c>
+      <c r="C194" t="s">
+        <v>100</v>
       </c>
       <c r="D194" t="n">
         <v>-9999</v>
@@ -8579,18 +9517,21 @@
         <v>-9999</v>
       </c>
       <c r="M194" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N194" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="B195" t="s">
-        <v>233</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-9999</v>
+        <v>249</v>
+      </c>
+      <c r="C195" t="s">
+        <v>100</v>
       </c>
       <c r="D195" t="n">
         <v>-9999</v>
@@ -8620,18 +9561,21 @@
         <v>-9999</v>
       </c>
       <c r="M195" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N195" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="B196" t="s">
-        <v>233</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-9999</v>
+        <v>249</v>
+      </c>
+      <c r="C196" t="s">
+        <v>100</v>
       </c>
       <c r="D196" t="n">
         <v>-9999</v>
@@ -8661,18 +9605,21 @@
         <v>-9999</v>
       </c>
       <c r="M196" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N196" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="B197" t="s">
-        <v>43</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-9999</v>
+        <v>82</v>
+      </c>
+      <c r="C197" t="s">
+        <v>100</v>
       </c>
       <c r="D197" t="n">
         <v>-9999</v>
@@ -8702,18 +9649,21 @@
         <v>-9999</v>
       </c>
       <c r="M197" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N197" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B198" t="s">
-        <v>245</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-9999</v>
+        <v>82</v>
+      </c>
+      <c r="C198" t="s">
+        <v>100</v>
       </c>
       <c r="D198" t="n">
         <v>-9999</v>
@@ -8743,18 +9693,21 @@
         <v>-9999</v>
       </c>
       <c r="M198" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N198" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="B199" t="s">
-        <v>245</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-9999</v>
+        <v>82</v>
+      </c>
+      <c r="C199" t="s">
+        <v>100</v>
       </c>
       <c r="D199" t="n">
         <v>-9999</v>
@@ -8784,18 +9737,21 @@
         <v>-9999</v>
       </c>
       <c r="M199" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N199" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="B200" t="s">
-        <v>245</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-9999</v>
+        <v>82</v>
+      </c>
+      <c r="C200" t="s">
+        <v>100</v>
       </c>
       <c r="D200" t="n">
         <v>-9999</v>
@@ -8825,18 +9781,21 @@
         <v>-9999</v>
       </c>
       <c r="M200" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N200" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="B201" t="s">
-        <v>245</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-9999</v>
+        <v>82</v>
+      </c>
+      <c r="C201" t="s">
+        <v>100</v>
       </c>
       <c r="D201" t="n">
         <v>-9999</v>
@@ -8866,18 +9825,21 @@
         <v>-9999</v>
       </c>
       <c r="M201" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N201" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="B202" t="s">
-        <v>245</v>
-      </c>
-      <c r="C202" t="n">
-        <v>-9999</v>
+        <v>265</v>
+      </c>
+      <c r="C202" t="s">
+        <v>100</v>
       </c>
       <c r="D202" t="n">
         <v>-9999</v>
@@ -8907,18 +9869,21 @@
         <v>-9999</v>
       </c>
       <c r="M202" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N202" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="B203" t="s">
-        <v>245</v>
-      </c>
-      <c r="C203" t="n">
-        <v>-9999</v>
+        <v>265</v>
+      </c>
+      <c r="C203" t="s">
+        <v>100</v>
       </c>
       <c r="D203" t="n">
         <v>-9999</v>
@@ -8948,18 +9913,21 @@
         <v>-9999</v>
       </c>
       <c r="M203" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N203" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="B204" t="s">
-        <v>245</v>
-      </c>
-      <c r="C204" t="n">
-        <v>-9999</v>
+        <v>265</v>
+      </c>
+      <c r="C204" t="s">
+        <v>100</v>
       </c>
       <c r="D204" t="n">
         <v>-9999</v>
@@ -8989,18 +9957,21 @@
         <v>-9999</v>
       </c>
       <c r="M204" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N204" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="B205" t="s">
-        <v>245</v>
-      </c>
-      <c r="C205" t="n">
-        <v>-9999</v>
+        <v>265</v>
+      </c>
+      <c r="C205" t="s">
+        <v>100</v>
       </c>
       <c r="D205" t="n">
         <v>-9999</v>
@@ -9030,18 +10001,21 @@
         <v>-9999</v>
       </c>
       <c r="M205" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N205" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B206" t="s">
-        <v>245</v>
-      </c>
-      <c r="C206" t="n">
-        <v>-9999</v>
+        <v>265</v>
+      </c>
+      <c r="C206" t="s">
+        <v>100</v>
       </c>
       <c r="D206" t="n">
         <v>-9999</v>
@@ -9071,18 +10045,21 @@
         <v>-9999</v>
       </c>
       <c r="M206" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N206" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="B207" t="s">
-        <v>245</v>
-      </c>
-      <c r="C207" t="n">
-        <v>-9999</v>
+        <v>265</v>
+      </c>
+      <c r="C207" t="s">
+        <v>100</v>
       </c>
       <c r="D207" t="n">
         <v>-9999</v>
@@ -9112,18 +10089,21 @@
         <v>-9999</v>
       </c>
       <c r="M207" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N207" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B208" t="s">
-        <v>79</v>
-      </c>
-      <c r="C208" t="n">
-        <v>-9999</v>
+        <v>265</v>
+      </c>
+      <c r="C208" t="s">
+        <v>100</v>
       </c>
       <c r="D208" t="n">
         <v>-9999</v>
@@ -9153,18 +10133,21 @@
         <v>-9999</v>
       </c>
       <c r="M208" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N208" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="B209" t="s">
-        <v>79</v>
-      </c>
-      <c r="C209" t="n">
-        <v>-9999</v>
+        <v>265</v>
+      </c>
+      <c r="C209" t="s">
+        <v>100</v>
       </c>
       <c r="D209" t="n">
         <v>-9999</v>
@@ -9194,18 +10177,21 @@
         <v>-9999</v>
       </c>
       <c r="M209" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N209" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="B210" t="s">
-        <v>79</v>
-      </c>
-      <c r="C210" t="n">
-        <v>-9999</v>
+        <v>265</v>
+      </c>
+      <c r="C210" t="s">
+        <v>100</v>
       </c>
       <c r="D210" t="n">
         <v>-9999</v>
@@ -9235,18 +10221,21 @@
         <v>-9999</v>
       </c>
       <c r="M210" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N210" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="B211" t="s">
-        <v>79</v>
-      </c>
-      <c r="C211" t="n">
-        <v>-9999</v>
+        <v>265</v>
+      </c>
+      <c r="C211" t="s">
+        <v>100</v>
       </c>
       <c r="D211" t="n">
         <v>-9999</v>
@@ -9276,18 +10265,21 @@
         <v>-9999</v>
       </c>
       <c r="M211" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N211" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="B212" t="s">
-        <v>79</v>
-      </c>
-      <c r="C212" t="n">
-        <v>-9999</v>
+        <v>80</v>
+      </c>
+      <c r="C212" t="s">
+        <v>100</v>
       </c>
       <c r="D212" t="n">
         <v>-9999</v>
@@ -9317,18 +10309,21 @@
         <v>-9999</v>
       </c>
       <c r="M212" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N212" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B213" t="s">
-        <v>261</v>
-      </c>
-      <c r="C213" t="n">
-        <v>-9999</v>
+        <v>80</v>
+      </c>
+      <c r="C213" t="s">
+        <v>100</v>
       </c>
       <c r="D213" t="n">
         <v>-9999</v>
@@ -9358,18 +10353,21 @@
         <v>-9999</v>
       </c>
       <c r="M213" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N213" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="B214" t="s">
-        <v>261</v>
-      </c>
-      <c r="C214" t="n">
-        <v>-9999</v>
+        <v>80</v>
+      </c>
+      <c r="C214" t="s">
+        <v>100</v>
       </c>
       <c r="D214" t="n">
         <v>-9999</v>
@@ -9399,18 +10397,21 @@
         <v>-9999</v>
       </c>
       <c r="M214" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N214" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="B215" t="s">
-        <v>261</v>
-      </c>
-      <c r="C215" t="n">
-        <v>-9999</v>
+        <v>80</v>
+      </c>
+      <c r="C215" t="s">
+        <v>100</v>
       </c>
       <c r="D215" t="n">
         <v>-9999</v>
@@ -9440,18 +10441,21 @@
         <v>-9999</v>
       </c>
       <c r="M215" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N215" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="B216" t="s">
-        <v>261</v>
-      </c>
-      <c r="C216" t="n">
-        <v>-9999</v>
+        <v>280</v>
+      </c>
+      <c r="C216" t="s">
+        <v>100</v>
       </c>
       <c r="D216" t="n">
         <v>-9999</v>
@@ -9481,18 +10485,21 @@
         <v>-9999</v>
       </c>
       <c r="M216" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N216" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="B217" t="s">
-        <v>261</v>
-      </c>
-      <c r="C217" t="n">
-        <v>-9999</v>
+        <v>280</v>
+      </c>
+      <c r="C217" t="s">
+        <v>100</v>
       </c>
       <c r="D217" t="n">
         <v>-9999</v>
@@ -9522,18 +10529,21 @@
         <v>-9999</v>
       </c>
       <c r="M217" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N217" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="B218" t="s">
-        <v>261</v>
-      </c>
-      <c r="C218" t="n">
-        <v>-9999</v>
+        <v>280</v>
+      </c>
+      <c r="C218" t="s">
+        <v>36</v>
       </c>
       <c r="D218" t="n">
         <v>-9999</v>
@@ -9563,18 +10573,21 @@
         <v>-9999</v>
       </c>
       <c r="M218" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N218" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B219" t="s">
-        <v>261</v>
-      </c>
-      <c r="C219" t="n">
-        <v>-9999</v>
+        <v>280</v>
+      </c>
+      <c r="C219" t="s">
+        <v>100</v>
       </c>
       <c r="D219" t="n">
         <v>-9999</v>
@@ -9604,18 +10617,21 @@
         <v>-9999</v>
       </c>
       <c r="M219" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N219" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="B220" t="s">
-        <v>261</v>
-      </c>
-      <c r="C220" t="n">
-        <v>-9999</v>
+        <v>280</v>
+      </c>
+      <c r="C220" t="s">
+        <v>100</v>
       </c>
       <c r="D220" t="n">
         <v>-9999</v>
@@ -9645,18 +10661,21 @@
         <v>-9999</v>
       </c>
       <c r="M220" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N220" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="B221" t="s">
-        <v>261</v>
-      </c>
-      <c r="C221" t="n">
-        <v>-9999</v>
+        <v>280</v>
+      </c>
+      <c r="C221" t="s">
+        <v>100</v>
       </c>
       <c r="D221" t="n">
         <v>-9999</v>
@@ -9686,18 +10705,21 @@
         <v>-9999</v>
       </c>
       <c r="M221" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N221" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="B222" t="s">
-        <v>261</v>
-      </c>
-      <c r="C222" t="n">
-        <v>-9999</v>
+        <v>280</v>
+      </c>
+      <c r="C222" t="s">
+        <v>100</v>
       </c>
       <c r="D222" t="n">
         <v>-9999</v>
@@ -9727,18 +10749,21 @@
         <v>-9999</v>
       </c>
       <c r="M222" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N222" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B223" t="s">
-        <v>77</v>
-      </c>
-      <c r="C223" t="n">
-        <v>-9999</v>
+        <v>280</v>
+      </c>
+      <c r="C223" t="s">
+        <v>100</v>
       </c>
       <c r="D223" t="n">
         <v>-9999</v>
@@ -9768,18 +10793,21 @@
         <v>-9999</v>
       </c>
       <c r="M223" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N223" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="B224" t="s">
-        <v>77</v>
-      </c>
-      <c r="C224" t="n">
-        <v>-9999</v>
+        <v>280</v>
+      </c>
+      <c r="C224" t="s">
+        <v>100</v>
       </c>
       <c r="D224" t="n">
         <v>-9999</v>
@@ -9809,18 +10837,21 @@
         <v>-9999</v>
       </c>
       <c r="M224" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N224" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="B225" t="s">
-        <v>77</v>
-      </c>
-      <c r="C225" t="n">
-        <v>-9999</v>
+        <v>280</v>
+      </c>
+      <c r="C225" t="s">
+        <v>100</v>
       </c>
       <c r="D225" t="n">
         <v>-9999</v>
@@ -9850,18 +10881,21 @@
         <v>-9999</v>
       </c>
       <c r="M225" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N225" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="B226" t="s">
-        <v>77</v>
-      </c>
-      <c r="C226" t="n">
-        <v>-9999</v>
+        <v>74</v>
+      </c>
+      <c r="C226" t="s">
+        <v>100</v>
       </c>
       <c r="D226" t="n">
         <v>-9999</v>
@@ -9891,18 +10925,21 @@
         <v>-9999</v>
       </c>
       <c r="M226" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N226" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="B227" t="s">
-        <v>276</v>
-      </c>
-      <c r="C227" t="n">
-        <v>-9999</v>
+        <v>74</v>
+      </c>
+      <c r="C227" t="s">
+        <v>100</v>
       </c>
       <c r="D227" t="n">
         <v>-9999</v>
@@ -9932,18 +10969,21 @@
         <v>-9999</v>
       </c>
       <c r="M227" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N227" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="B228" t="s">
-        <v>276</v>
-      </c>
-      <c r="C228" t="n">
-        <v>-9999</v>
+        <v>74</v>
+      </c>
+      <c r="C228" t="s">
+        <v>100</v>
       </c>
       <c r="D228" t="n">
         <v>-9999</v>
@@ -9973,18 +11013,21 @@
         <v>-9999</v>
       </c>
       <c r="M228" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N228" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="B229" t="s">
-        <v>276</v>
-      </c>
-      <c r="C229" t="n">
-        <v>-9999</v>
+        <v>74</v>
+      </c>
+      <c r="C229" t="s">
+        <v>100</v>
       </c>
       <c r="D229" t="n">
         <v>-9999</v>
@@ -10014,18 +11057,21 @@
         <v>-9999</v>
       </c>
       <c r="M229" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N229" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="B230" t="s">
-        <v>276</v>
-      </c>
-      <c r="C230" t="n">
-        <v>-9999</v>
+        <v>74</v>
+      </c>
+      <c r="C230" t="s">
+        <v>100</v>
       </c>
       <c r="D230" t="n">
         <v>-9999</v>
@@ -10055,18 +11101,21 @@
         <v>-9999</v>
       </c>
       <c r="M230" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N230" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="B231" t="s">
-        <v>276</v>
-      </c>
-      <c r="C231" t="n">
-        <v>-9999</v>
+        <v>78</v>
+      </c>
+      <c r="C231" t="s">
+        <v>100</v>
       </c>
       <c r="D231" t="n">
         <v>-9999</v>
@@ -10096,18 +11145,21 @@
         <v>-9999</v>
       </c>
       <c r="M231" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N231" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="B232" t="s">
-        <v>276</v>
-      </c>
-      <c r="C232" t="n">
-        <v>-9999</v>
+        <v>78</v>
+      </c>
+      <c r="C232" t="s">
+        <v>100</v>
       </c>
       <c r="D232" t="n">
         <v>-9999</v>
@@ -10137,18 +11189,21 @@
         <v>-9999</v>
       </c>
       <c r="M232" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N232" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="B233" t="s">
-        <v>276</v>
-      </c>
-      <c r="C233" t="n">
-        <v>-9999</v>
+        <v>78</v>
+      </c>
+      <c r="C233" t="s">
+        <v>100</v>
       </c>
       <c r="D233" t="n">
         <v>-9999</v>
@@ -10178,18 +11233,21 @@
         <v>-9999</v>
       </c>
       <c r="M233" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N233" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="B234" t="s">
-        <v>276</v>
-      </c>
-      <c r="C234" t="n">
-        <v>-9999</v>
+        <v>74</v>
+      </c>
+      <c r="C234" t="s">
+        <v>100</v>
       </c>
       <c r="D234" t="n">
         <v>-9999</v>
@@ -10219,18 +11277,21 @@
         <v>-9999</v>
       </c>
       <c r="M234" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N234" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="B235" t="s">
-        <v>276</v>
-      </c>
-      <c r="C235" t="n">
-        <v>-9999</v>
+        <v>105</v>
+      </c>
+      <c r="C235" t="s">
+        <v>100</v>
       </c>
       <c r="D235" t="n">
         <v>-9999</v>
@@ -10260,18 +11321,21 @@
         <v>-9999</v>
       </c>
       <c r="M235" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N235" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="B236" t="s">
-        <v>276</v>
-      </c>
-      <c r="C236" t="n">
-        <v>-9999</v>
+        <v>112</v>
+      </c>
+      <c r="C236" t="s">
+        <v>100</v>
       </c>
       <c r="D236" t="n">
         <v>-9999</v>
@@ -10301,18 +11365,21 @@
         <v>-9999</v>
       </c>
       <c r="M236" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N236" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="B237" t="s">
-        <v>71</v>
-      </c>
-      <c r="C237" t="n">
-        <v>-9999</v>
+        <v>169</v>
+      </c>
+      <c r="C237" t="s">
+        <v>100</v>
       </c>
       <c r="D237" t="n">
         <v>-9999</v>
@@ -10342,18 +11409,21 @@
         <v>-9999</v>
       </c>
       <c r="M237" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N237" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="B238" t="s">
-        <v>71</v>
-      </c>
-      <c r="C238" t="n">
-        <v>-9999</v>
+        <v>159</v>
+      </c>
+      <c r="C238" t="s">
+        <v>100</v>
       </c>
       <c r="D238" t="n">
         <v>-9999</v>
@@ -10383,18 +11453,21 @@
         <v>-9999</v>
       </c>
       <c r="M238" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N238" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="B239" t="s">
-        <v>71</v>
-      </c>
-      <c r="C239" t="n">
-        <v>-9999</v>
+        <v>129</v>
+      </c>
+      <c r="C239" t="s">
+        <v>100</v>
       </c>
       <c r="D239" t="n">
         <v>-9999</v>
@@ -10424,18 +11497,21 @@
         <v>-9999</v>
       </c>
       <c r="M239" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N239" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="B240" t="s">
-        <v>71</v>
-      </c>
-      <c r="C240" t="n">
-        <v>-9999</v>
+        <v>141</v>
+      </c>
+      <c r="C240" t="s">
+        <v>100</v>
       </c>
       <c r="D240" t="n">
         <v>-9999</v>
@@ -10465,18 +11541,21 @@
         <v>-9999</v>
       </c>
       <c r="M240" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N240" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="B241" t="s">
-        <v>71</v>
-      </c>
-      <c r="C241" t="n">
-        <v>-9999</v>
+        <v>119</v>
+      </c>
+      <c r="C241" t="s">
+        <v>100</v>
       </c>
       <c r="D241" t="n">
         <v>-9999</v>
@@ -10506,18 +11585,21 @@
         <v>-9999</v>
       </c>
       <c r="M241" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N241" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B242" t="s">
-        <v>75</v>
-      </c>
-      <c r="C242" t="n">
-        <v>-9999</v>
+        <v>86</v>
+      </c>
+      <c r="C242" t="s">
+        <v>36</v>
       </c>
       <c r="D242" t="n">
         <v>-9999</v>
@@ -10547,18 +11629,21 @@
         <v>-9999</v>
       </c>
       <c r="M242" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N242" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="B243" t="s">
-        <v>75</v>
-      </c>
-      <c r="C243" t="n">
-        <v>-9999</v>
+        <v>74</v>
+      </c>
+      <c r="C243" t="s">
+        <v>100</v>
       </c>
       <c r="D243" t="n">
         <v>-9999</v>
@@ -10588,18 +11673,21 @@
         <v>-9999</v>
       </c>
       <c r="M243" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N243" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="B244" t="s">
-        <v>75</v>
-      </c>
-      <c r="C244" t="n">
-        <v>-9999</v>
+        <v>42</v>
+      </c>
+      <c r="C244" t="s">
+        <v>100</v>
       </c>
       <c r="D244" t="n">
         <v>-9999</v>
@@ -10629,18 +11717,21 @@
         <v>-9999</v>
       </c>
       <c r="M244" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N244" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="B245" t="s">
-        <v>71</v>
-      </c>
-      <c r="C245" t="n">
-        <v>-9999</v>
+        <v>206</v>
+      </c>
+      <c r="C245" t="s">
+        <v>100</v>
       </c>
       <c r="D245" t="n">
         <v>-9999</v>
@@ -10670,18 +11761,21 @@
         <v>-9999</v>
       </c>
       <c r="M245" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N245" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="B246" t="s">
-        <v>101</v>
-      </c>
-      <c r="C246" t="n">
-        <v>-9999</v>
+        <v>217</v>
+      </c>
+      <c r="C246" t="s">
+        <v>100</v>
       </c>
       <c r="D246" t="n">
         <v>-9999</v>
@@ -10711,18 +11805,21 @@
         <v>-9999</v>
       </c>
       <c r="M246" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N246" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="B247" t="s">
-        <v>108</v>
-      </c>
-      <c r="C247" t="n">
-        <v>-9999</v>
+        <v>229</v>
+      </c>
+      <c r="C247" t="s">
+        <v>100</v>
       </c>
       <c r="D247" t="n">
         <v>-9999</v>
@@ -10752,18 +11849,21 @@
         <v>-9999</v>
       </c>
       <c r="M247" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N247" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="B248" t="s">
-        <v>165</v>
-      </c>
-      <c r="C248" t="n">
-        <v>-9999</v>
+        <v>237</v>
+      </c>
+      <c r="C248" t="s">
+        <v>100</v>
       </c>
       <c r="D248" t="n">
         <v>-9999</v>
@@ -10793,18 +11893,21 @@
         <v>-9999</v>
       </c>
       <c r="M248" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N248" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="B249" t="s">
-        <v>155</v>
-      </c>
-      <c r="C249" t="n">
-        <v>-9999</v>
+        <v>249</v>
+      </c>
+      <c r="C249" t="s">
+        <v>100</v>
       </c>
       <c r="D249" t="n">
         <v>-9999</v>
@@ -10834,18 +11937,21 @@
         <v>-9999</v>
       </c>
       <c r="M249" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N249" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="B250" t="s">
-        <v>125</v>
-      </c>
-      <c r="C250" t="n">
-        <v>-9999</v>
+        <v>265</v>
+      </c>
+      <c r="C250" t="s">
+        <v>100</v>
       </c>
       <c r="D250" t="n">
         <v>-9999</v>
@@ -10875,18 +11981,21 @@
         <v>-9999</v>
       </c>
       <c r="M250" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N250" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="B251" t="s">
-        <v>137</v>
-      </c>
-      <c r="C251" t="n">
-        <v>-9999</v>
+        <v>80</v>
+      </c>
+      <c r="C251" t="s">
+        <v>100</v>
       </c>
       <c r="D251" t="n">
         <v>-9999</v>
@@ -10916,18 +12025,21 @@
         <v>-9999</v>
       </c>
       <c r="M251" t="n">
+        <v>-9999</v>
+      </c>
+      <c r="N251" t="n">
         <v>-9999</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="B252" t="s">
-        <v>115</v>
-      </c>
-      <c r="C252" t="n">
-        <v>-9999</v>
+        <v>280</v>
+      </c>
+      <c r="C252" t="s">
+        <v>100</v>
       </c>
       <c r="D252" t="n">
         <v>-9999</v>
@@ -10959,455 +12071,7 @@
       <c r="M252" t="n">
         <v>-9999</v>
       </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="s">
-        <v>302</v>
-      </c>
-      <c r="B253" t="s">
-        <v>83</v>
-      </c>
-      <c r="C253" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="D253" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="E253" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="F253" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="G253" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="H253" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="I253" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="J253" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="K253" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="L253" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="M253" t="n">
-        <v>-9999</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="s">
-        <v>303</v>
-      </c>
-      <c r="B254" t="s">
-        <v>71</v>
-      </c>
-      <c r="C254" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="D254" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="E254" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="F254" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="G254" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="H254" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="I254" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="J254" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="K254" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="L254" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="M254" t="n">
-        <v>-9999</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="s">
-        <v>304</v>
-      </c>
-      <c r="B255" t="s">
-        <v>39</v>
-      </c>
-      <c r="C255" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="D255" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="E255" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="F255" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="G255" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="H255" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="I255" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="J255" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="K255" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="L255" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="M255" t="n">
-        <v>-9999</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="s">
-        <v>305</v>
-      </c>
-      <c r="B256" t="s">
-        <v>202</v>
-      </c>
-      <c r="C256" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="D256" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="E256" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="F256" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="G256" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="H256" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="I256" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="J256" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="K256" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="L256" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="M256" t="n">
-        <v>-9999</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="s">
-        <v>306</v>
-      </c>
-      <c r="B257" t="s">
-        <v>213</v>
-      </c>
-      <c r="C257" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="D257" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="E257" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="F257" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="G257" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="H257" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="I257" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="J257" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="K257" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="L257" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="M257" t="n">
-        <v>-9999</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="s">
-        <v>307</v>
-      </c>
-      <c r="B258" t="s">
-        <v>225</v>
-      </c>
-      <c r="C258" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="D258" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="E258" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="F258" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="G258" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="H258" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="I258" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="J258" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="K258" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="L258" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="M258" t="n">
-        <v>-9999</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="s">
-        <v>308</v>
-      </c>
-      <c r="B259" t="s">
-        <v>233</v>
-      </c>
-      <c r="C259" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="D259" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="E259" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="F259" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="G259" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="H259" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="I259" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="J259" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="K259" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="L259" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="M259" t="n">
-        <v>-9999</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="s">
-        <v>309</v>
-      </c>
-      <c r="B260" t="s">
-        <v>245</v>
-      </c>
-      <c r="C260" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="D260" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="E260" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="F260" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="G260" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="H260" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="I260" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="J260" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="K260" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="L260" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="M260" t="n">
-        <v>-9999</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="s">
-        <v>310</v>
-      </c>
-      <c r="B261" t="s">
-        <v>261</v>
-      </c>
-      <c r="C261" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="D261" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="E261" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="F261" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="G261" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="H261" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="I261" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="J261" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="K261" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="L261" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="M261" t="n">
-        <v>-9999</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="s">
-        <v>311</v>
-      </c>
-      <c r="B262" t="s">
-        <v>77</v>
-      </c>
-      <c r="C262" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="D262" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="E262" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="F262" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="G262" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="H262" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="I262" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="J262" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="K262" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="L262" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="M262" t="n">
-        <v>-9999</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="s">
-        <v>312</v>
-      </c>
-      <c r="B263" t="s">
-        <v>276</v>
-      </c>
-      <c r="C263" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="D263" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="E263" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="F263" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="G263" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="H263" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="I263" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="J263" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="K263" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="L263" t="n">
-        <v>-9999</v>
-      </c>
-      <c r="M263" t="n">
+      <c r="N252" t="n">
         <v>-9999</v>
       </c>
     </row>
